--- a/languages/pt/output/import/葡萄牙语专四基础.xlsx
+++ b/languages/pt/output/import/葡萄牙语专四基础.xlsx
@@ -34219,7 +34219,7 @@
       </c>
       <c r="B1057" s="1" t="inlineStr">
         <is>
-          <t>[pɛʁˈdɐ̃w̃/ [pɛɦˈdɐ̃ʊ̯̃]] 宽恕&lt;名&gt;</t>
+          <t>[pɛʁˈdɐ̃w̃] 宽恕&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1057" s="1" t="inlineStr">

--- a/languages/pt/output/import/葡萄牙语专四基础.xlsx
+++ b/languages/pt/output/import/葡萄牙语专四基础.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>[ũ̃] 一个（阳性）&lt;限定&gt;</t>
+          <t>[ũ̃] 一个[阳性]&lt;限定&gt;</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>一个（阳性）</t>
+          <t>一个[阳性]</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>[obɾiˈgadu] 谢谢（男用）&lt;叹&gt;</t>
+          <t>[obɾiˈgadu] 谢谢[男用]&lt;叹&gt;</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>谢谢（男用）</t>
+          <t>谢谢[男用]</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>[seˈɲoɾ] 先生。&lt;名&gt;</t>
+          <t>[seˈɲoɾ] 先生&lt;名&gt;</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
-          <t>[obɾiˈgadɐ] 谢谢（女用）&lt;叹&gt;</t>
+          <t>[obɾiˈgadɐ] 谢谢[女用]&lt;叹&gt;</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="D185" s="1" t="inlineStr">
         <is>
-          <t>谢谢（女用）</t>
+          <t>谢谢[女用]</t>
         </is>
       </c>
       <c r="E185" s="1" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t>[iˈa] ia&lt;名&gt;</t>
+          <t>[iˈa] 人工智能；AI&lt;名&gt;</t>
         </is>
       </c>
       <c r="C219" s="1" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="D219" s="1" t="inlineStr">
         <is>
-          <t>ia</t>
+          <t>人工智能</t>
         </is>
       </c>
       <c r="E219" s="1" t="inlineStr">
@@ -10127,7 +10127,7 @@
       </c>
       <c r="B304" s="1" t="inlineStr">
         <is>
-          <t>[doˈtɔɾ] 博士。&lt;名&gt;</t>
+          <t>[doˈtɔɾ] 博士&lt;名&gt;</t>
         </is>
       </c>
       <c r="C304" s="1" t="inlineStr">
@@ -11343,7 +11343,7 @@
       </c>
       <c r="B342" s="1" t="inlineStr">
         <is>
-          <t>[seˈɲoɾa] 夫人。&lt;名&gt;</t>
+          <t>[seˈɲoɾa] 夫人&lt;名&gt;</t>
         </is>
       </c>
       <c r="C342" s="1" t="inlineStr">
@@ -47711,7 +47711,7 @@
       </c>
       <c r="B1479" s="1" t="inlineStr">
         <is>
-          <t>[sɛˈɡʊ̃du] s。&lt;名&gt;</t>
+          <t>[sɛˈɡʊ̃du] 秒；秒钟&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1479" s="1" t="inlineStr">
@@ -47721,7 +47721,7 @@
       </c>
       <c r="D1479" s="1" t="inlineStr">
         <is>
-          <t>s。</t>
+          <t>秒</t>
         </is>
       </c>
       <c r="E1479" s="1" t="inlineStr">

--- a/languages/pt/output/import/葡萄牙语专四基础.xlsx
+++ b/languages/pt/output/import/葡萄牙语专四基础.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +440,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ki</t>
+          <t>/ki/</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -472,7 +472,7 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>nãw̃</t>
+          <t>/nãw̃/</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -504,7 +504,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>dʒi</t>
+          <t>/dʒi/</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>ũ̃</t>
+          <t>/ũ̃/</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>paɾɐ</t>
+          <t>/paɾɐ/</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>ew</t>
+          <t>/ew/</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>kõ̃</t>
+          <t>/kõ̃/</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>puɾ</t>
+          <t>/puɾ/</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>[us] 的&lt;代&gt;</t>
+          <t>[us] 这些；那些&lt;代&gt;</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>的</t>
+          <t>这些；那些</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>mas</t>
+          <t>/mas/</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>ẽ̃</t>
+          <t>/ẽ̃/</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>bẽ̃j</t>
+          <t>/bẽ̃j/</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>ˈisu</t>
+          <t>/ˈisu/</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>/da/</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>kɐˈmu</t>
+          <t>/kɐˈmu/</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>[as] 的&lt;代&gt;</t>
+          <t>[as] 这些；那些&lt;代&gt;</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>的</t>
+          <t>这些；那些</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>nu</t>
+          <t>/nu/</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>majs</t>
+          <t>/majs/</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>mew</t>
+          <t>/mew/</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>ɐˈki</t>
+          <t>/ɐˈki/</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>muj̃tu</t>
+          <t>/muj̃tu/</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>ˈɛ.lə</t>
+          <t>/ˈɛ.lə/</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>ˈistu</t>
+          <t>/ˈistu/</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>ʒɐ</t>
+          <t>/ʒɐ/</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>[ˈsɔ] 独自一人&lt;形&gt;</t>
+          <t>[/ˈsɔ/] 只，仅仅；单独的&lt;副/形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>独自一人</t>
+          <t>只，仅仅；单独的&lt;副/形&gt;</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>ˈtudu</t>
+          <t>/ˈtudu/</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>puɾˈke</t>
+          <t>/puɾˈke/</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>kwɐ̃du</t>
+          <t>/kwɐ̃du/</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>voˈse</t>
+          <t>/voˈse/</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>ˈɔndʒi</t>
+          <t>/ˈɔndʒi/</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>ˈnadɐ</t>
+          <t>/ˈnadɐ/</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>ow</t>
+          <t>/ow/</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>sew</t>
+          <t>/sew/</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>[poˈdeʁ] 电源&lt;名&gt;</t>
+          <t>[poˈdeʁ] 能；可以；权力&lt;名&gt;</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>电源</t>
+          <t>能；可以；权力</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>ˈelis</t>
+          <t>/ˈelis/</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>ˈnʊs</t>
+          <t>/ˈnʊs/</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>ˈnũkɐ</t>
+          <t>/ˈnũkɐ/</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>tɐ̃ˈbɐ̃j</t>
+          <t>/tɐ̃ˈbɐ̃j/</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>[ˈtɐ̃w̃] 所以&lt;动&gt;</t>
+          <t>[ˈtɐ̃w̃] 如此；这么；那么&lt;动&gt;</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>所以</t>
+          <t>如此；这么；那么</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>ɔˈla</t>
+          <t>/ɔˈla/</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>obɾiˈgadu</t>
+          <t>/obɾiˈgadu/</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>tʃi</t>
+          <t>/tʃi/</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>ˈsẽpɾi</t>
+          <t>/ˈsẽpɾi/</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>ˈaw̃gu</t>
+          <t>/ˈaw̃gu/</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>[ˈpe.lu] 毛皮&lt;名&gt;</t>
+          <t>[/ˈpe.lu/] 毛；皮毛（pelo 的名词义）；另为 por+o 的缩合形式&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>毛皮</t>
+          <t>毛；皮毛（pelo 的名词义）；另为 por+o 的缩合形式</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>[pa.ɾeˈseʁ] 意见&lt;名&gt;</t>
+          <t>[/pa.ɾeˈseʁ/] 似乎；看法&lt;动/名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
-          <t>意见</t>
+          <t>似乎；看法&lt;动/名&gt;</t>
         </is>
       </c>
       <c r="E114" s="1" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>seˈɲoɾ</t>
+          <t>/seˈɲoɾ/</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>[ˈkwaw] 其中&lt;代&gt;</t>
+          <t>[ˈkwaw] 哪个；哪些&lt;代&gt;</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>其中</t>
+          <t>哪个；哪些</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>mewʃ</t>
+          <t>/mewʃ/</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>/o/</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>[kõˈsi.ɡu] 我可以&lt;副&gt;</t>
+          <t>[kõˈsi.ɡu] 同自己一起；随身&lt;副&gt;</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t>我可以</t>
+          <t>同自己一起；随身</t>
         </is>
       </c>
       <c r="E167" s="1" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>[ˈtɾe(j)s] 三&lt;名&gt;</t>
+          <t>[/ˈtɾe(j)s/] 三&lt;数&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t>三</t>
+          <t>三&lt;数&gt;</t>
         </is>
       </c>
       <c r="E168" s="1" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>[puʁˈke] 为什么&lt;名&gt;</t>
+          <t>[/puʁˈke/] 原因&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="D175" s="1" t="inlineStr">
         <is>
-          <t>为什么</t>
+          <t>原因&lt;名&gt;</t>
         </is>
       </c>
       <c r="E175" s="1" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="C185" s="1" t="inlineStr">
         <is>
-          <t>obɾiˈgadɐ</t>
+          <t>/obɾiˈgadɐ/</t>
         </is>
       </c>
       <c r="D185" s="1" t="inlineStr">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>[pɾiˈme(j).ɾu] 第一&lt;名&gt;</t>
+          <t>[/pɾiˈme(j).ɾu/] 第一的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="D186" s="1" t="inlineStr">
         <is>
-          <t>第一</t>
+          <t>第一的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E186" s="1" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>[keˈɾi.du] 亲爱的&lt;名&gt;</t>
+          <t>[/keˈɾi.du/] 亲爱的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="D198" s="1" t="inlineStr">
         <is>
-          <t>亲爱的</t>
+          <t>亲爱的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E198" s="1" t="inlineStr">
@@ -6835,7 +6835,7 @@
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>[ˈsi] 是的&lt;名&gt;</t>
+          <t>[ˈsi] 自己；本身&lt;名&gt;</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="D201" s="1" t="inlineStr">
         <is>
-          <t>是的</t>
+          <t>自己；本身</t>
         </is>
       </c>
       <c r="E201" s="1" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
-          <t>[ˌɔˈkej] 好的&lt;名&gt;</t>
+          <t>[/ˌɔˈkej/] 好的&lt;叹&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C209" s="1" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="D209" s="1" t="inlineStr">
         <is>
-          <t>好的</t>
+          <t>好的&lt;叹&gt;</t>
         </is>
       </c>
       <c r="E209" s="1" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t>[ˈfo.ɾɐ̃w̃] 是&lt;动&gt;</t>
+          <t>[ˈfo.ɾɐ̃w̃] 曾是；去了&lt;动&gt;</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="D218" s="1" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>曾是；去了</t>
         </is>
       </c>
       <c r="E218" s="1" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t>[iˈa] 人工智能；AI&lt;名&gt;</t>
+          <t>[/iˈa/] 去（ir 的陈述式过去未完成时第一/第三人称单数）&lt;动&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C219" s="1" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="D219" s="1" t="inlineStr">
         <is>
-          <t>人工智能</t>
+          <t>去（ir 的陈述式过去未完成时第一/第三人称单数）&lt;动&gt;</t>
         </is>
       </c>
       <c r="E219" s="1" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="C228" s="1" t="inlineStr">
         <is>
-          <t>se.ˈɾi.ə</t>
+          <t>/se.ˈɾi.ə/</t>
         </is>
       </c>
       <c r="D228" s="1" t="inlineStr">
@@ -8374,7 +8374,11 @@
           <t>太棒了&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C249" s="1" t="inlineStr"/>
+      <c r="C249" s="1" t="inlineStr">
+        <is>
+          <t>/ˈɔp.ti.mu/</t>
+        </is>
+      </c>
       <c r="D249" s="1" t="inlineStr">
         <is>
           <t>太棒了</t>
@@ -9615,7 +9619,7 @@
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t>[ˈpɛʁ.tu] 关闭&lt;副&gt;</t>
+          <t>[ˈpɛʁ.tu] 近；在附近&lt;副&gt;</t>
         </is>
       </c>
       <c r="C288" s="1" t="inlineStr">
@@ -9625,7 +9629,7 @@
       </c>
       <c r="D288" s="1" t="inlineStr">
         <is>
-          <t>关闭</t>
+          <t>近；在附近</t>
         </is>
       </c>
       <c r="E288" s="1" t="inlineStr">
@@ -10132,7 +10136,7 @@
       </c>
       <c r="C304" s="1" t="inlineStr">
         <is>
-          <t>doˈtɔɾ</t>
+          <t>/doˈtɔɾ/</t>
         </is>
       </c>
       <c r="D304" s="1" t="inlineStr">
@@ -10191,7 +10195,7 @@
       </c>
       <c r="B306" s="1" t="inlineStr">
         <is>
-          <t>[ˈtɛ.ʁɐ] 地球&lt;名&gt;</t>
+          <t>[/ˈtɛ.ʁɐ/] 土地；大地；地球&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C306" s="1" t="inlineStr">
@@ -10201,7 +10205,7 @@
       </c>
       <c r="D306" s="1" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>土地；大地；地球&lt;名&gt;</t>
         </is>
       </c>
       <c r="E306" s="1" t="inlineStr">
@@ -10452,7 +10456,7 @@
       </c>
       <c r="C314" s="1" t="inlineStr">
         <is>
-          <t>ˈpa.ɾə</t>
+          <t>/ˈpa.ɾə/</t>
         </is>
       </c>
       <c r="D314" s="1" t="inlineStr">
@@ -10703,7 +10707,7 @@
       </c>
       <c r="B322" s="1" t="inlineStr">
         <is>
-          <t>[viˈve(ʁ)] 直播&lt;名&gt;</t>
+          <t>[viˈve(ʁ)] 生活；活着；居住&lt;名&gt;</t>
         </is>
       </c>
       <c r="C322" s="1" t="inlineStr">
@@ -10713,7 +10717,7 @@
       </c>
       <c r="D322" s="1" t="inlineStr">
         <is>
-          <t>直播</t>
+          <t>生活；活着；居住</t>
         </is>
       </c>
       <c r="E322" s="1" t="inlineStr">
@@ -10767,7 +10771,7 @@
       </c>
       <c r="B324" s="1" t="inlineStr">
         <is>
-          <t>[paˈɾa(ʁ)] 帕拉尔&lt;动&gt;</t>
+          <t>[paˈɾa(ʁ)] 停止；停下&lt;动&gt;</t>
         </is>
       </c>
       <c r="C324" s="1" t="inlineStr">
@@ -10777,7 +10781,7 @@
       </c>
       <c r="D324" s="1" t="inlineStr">
         <is>
-          <t>帕拉尔</t>
+          <t>停止；停下</t>
         </is>
       </c>
       <c r="E324" s="1" t="inlineStr">
@@ -11348,7 +11352,7 @@
       </c>
       <c r="C342" s="1" t="inlineStr">
         <is>
-          <t>seˈɲoɾa</t>
+          <t>/seˈɲoɾa/</t>
         </is>
       </c>
       <c r="D342" s="1" t="inlineStr">
@@ -11535,7 +11539,7 @@
       </c>
       <c r="B348" s="1" t="inlineStr">
         <is>
-          <t>[ˈviw] 锯&lt;叹&gt;</t>
+          <t>[ˈviw] 看见；看到&lt;叹&gt;</t>
         </is>
       </c>
       <c r="C348" s="1" t="inlineStr">
@@ -11545,7 +11549,7 @@
       </c>
       <c r="D348" s="1" t="inlineStr">
         <is>
-          <t>锯</t>
+          <t>看见；看到</t>
         </is>
       </c>
       <c r="E348" s="1" t="inlineStr">
@@ -11567,7 +11571,7 @@
       </c>
       <c r="B349" s="1" t="inlineStr">
         <is>
-          <t>[iʁˈmɐ̃] 妹妹&lt;名&gt;</t>
+          <t>[/iʁˈmɐ̃/] 姐妹；姐姐/妹妹&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C349" s="1" t="inlineStr">
@@ -11577,7 +11581,7 @@
       </c>
       <c r="D349" s="1" t="inlineStr">
         <is>
-          <t>妹妹</t>
+          <t>姐妹；姐姐/妹妹&lt;名&gt;</t>
         </is>
       </c>
       <c r="E349" s="1" t="inlineStr">
@@ -11668,7 +11672,7 @@
       </c>
       <c r="C352" s="1" t="inlineStr">
         <is>
-          <t>ˈelɐs</t>
+          <t>/ˈelɐs/</t>
         </is>
       </c>
       <c r="D352" s="1" t="inlineStr">
@@ -11951,7 +11955,7 @@
       </c>
       <c r="B361" s="1" t="inlineStr">
         <is>
-          <t>[peˈd͡ʒi(ʁ)] 问&lt;动&gt;</t>
+          <t>[peˈd͡ʒi(ʁ)] 请求；要求；点餐&lt;动&gt;</t>
         </is>
       </c>
       <c r="C361" s="1" t="inlineStr">
@@ -11961,7 +11965,7 @@
       </c>
       <c r="D361" s="1" t="inlineStr">
         <is>
-          <t>问</t>
+          <t>请求；要求；点餐</t>
         </is>
       </c>
       <c r="E361" s="1" t="inlineStr">
@@ -12399,7 +12403,7 @@
       </c>
       <c r="B375" s="1" t="inlineStr">
         <is>
-          <t>[ʒɐ̃ˈta(ʁ)] 晚餐&lt;名&gt;</t>
+          <t>[/ʒɐ̃ˈta(ʁ)/] 吃晚餐&lt;动&gt;；晚餐&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C375" s="1" t="inlineStr">
@@ -12409,7 +12413,7 @@
       </c>
       <c r="D375" s="1" t="inlineStr">
         <is>
-          <t>晚餐</t>
+          <t>吃晚餐&lt;动&gt;；晚餐&lt;名&gt;</t>
         </is>
       </c>
       <c r="E375" s="1" t="inlineStr">
@@ -12820,7 +12824,7 @@
       </c>
       <c r="C388" s="1" t="inlineStr">
         <is>
-          <t>e.za.ta.ˈmẽ.tʃɪ</t>
+          <t>/e.za.ta.ˈmẽ.tʃɪ/</t>
         </is>
       </c>
       <c r="D388" s="1" t="inlineStr">
@@ -13583,7 +13587,7 @@
       </c>
       <c r="B412" s="1" t="inlineStr">
         <is>
-          <t>[d͡ʒiˈmajs] 太多了&lt;形&gt;</t>
+          <t>[/d͡ʒiˈmajs/] 太多&lt;副&gt;；其余的&lt;代&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C412" s="1" t="inlineStr">
@@ -13593,7 +13597,7 @@
       </c>
       <c r="D412" s="1" t="inlineStr">
         <is>
-          <t>太多了</t>
+          <t>太多&lt;副&gt;；其余的&lt;代&gt;</t>
         </is>
       </c>
       <c r="E412" s="1" t="inlineStr">
@@ -13679,7 +13683,7 @@
       </c>
       <c r="B415" s="1" t="inlineStr">
         <is>
-          <t>[seˈɡi(ʁ)] 关注&lt;动&gt;</t>
+          <t>[/seˈɡi(ʁ)/] 跟随；遵循&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C415" s="1" t="inlineStr">
@@ -13689,7 +13693,7 @@
       </c>
       <c r="D415" s="1" t="inlineStr">
         <is>
-          <t>关注</t>
+          <t>跟随；遵循&lt;动&gt;</t>
         </is>
       </c>
       <c r="E415" s="1" t="inlineStr">
@@ -13743,7 +13747,7 @@
       </c>
       <c r="B417" s="1" t="inlineStr">
         <is>
-          <t>[ˈpɾɔ.pɾju] 拥有&lt;形&gt;</t>
+          <t>[ˈpɾɔ.pɾju] 自己的；本身的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C417" s="1" t="inlineStr">
@@ -13753,7 +13757,7 @@
       </c>
       <c r="D417" s="1" t="inlineStr">
         <is>
-          <t>拥有</t>
+          <t>自己的；本身的</t>
         </is>
       </c>
       <c r="E417" s="1" t="inlineStr">
@@ -13935,7 +13939,7 @@
       </c>
       <c r="B423" s="1" t="inlineStr">
         <is>
-          <t>[ˈpɾɔ.si.mu] 下一个&lt;名&gt;</t>
+          <t>[/ˈpɾɔ.si.mu/] 下一个的；附近的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C423" s="1" t="inlineStr">
@@ -13945,7 +13949,7 @@
       </c>
       <c r="D423" s="1" t="inlineStr">
         <is>
-          <t>下一个</t>
+          <t>下一个的；附近的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E423" s="1" t="inlineStr">
@@ -14095,7 +14099,7 @@
       </c>
       <c r="B428" s="1" t="inlineStr">
         <is>
-          <t>[ˈʁɛs.tu] 休息&lt;名&gt;</t>
+          <t>[ˈʁɛs.tu] 其余；剩余部分&lt;名&gt;</t>
         </is>
       </c>
       <c r="C428" s="1" t="inlineStr">
@@ -14105,7 +14109,7 @@
       </c>
       <c r="D428" s="1" t="inlineStr">
         <is>
-          <t>休息</t>
+          <t>其余；剩余部分</t>
         </is>
       </c>
       <c r="E428" s="1" t="inlineStr">
@@ -14191,7 +14195,7 @@
       </c>
       <c r="B431" s="1" t="inlineStr">
         <is>
-          <t>[ˈsi.t͡ʃju] 站点&lt;名&gt;</t>
+          <t>[ˈsi.t͡ʃju] 地方；地点&lt;名&gt;</t>
         </is>
       </c>
       <c r="C431" s="1" t="inlineStr">
@@ -14201,7 +14205,7 @@
       </c>
       <c r="D431" s="1" t="inlineStr">
         <is>
-          <t>站点</t>
+          <t>地方；地点</t>
         </is>
       </c>
       <c r="E431" s="1" t="inlineStr">
@@ -14383,7 +14387,7 @@
       </c>
       <c r="B437" s="1" t="inlineStr">
         <is>
-          <t>[d͡ʒiˈɾej.tu] 对&lt;名&gt;</t>
+          <t>[d͡ʒiˈɾej.tu] 权利；法律；右边的&lt;名&gt;</t>
         </is>
       </c>
       <c r="C437" s="1" t="inlineStr">
@@ -14393,7 +14397,7 @@
       </c>
       <c r="D437" s="1" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>权利；法律；右边的</t>
         </is>
       </c>
       <c r="E437" s="1" t="inlineStr">
@@ -14767,7 +14771,7 @@
       </c>
       <c r="B449" s="1" t="inlineStr">
         <is>
-          <t>[ˈẽ.mi ˈɛ.ʁi] 先生&lt;名&gt;</t>
+          <t>[/ˈẽ.mi ˈɛ.ʁi/] 先生&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C449" s="1" t="inlineStr">
@@ -16559,7 +16563,7 @@
       </c>
       <c r="B505" s="1" t="inlineStr">
         <is>
-          <t>[ˈli.vɾi] 免费&lt;名&gt;</t>
+          <t>[ˈli.vɾi] 自由的；空闲的；免费的&lt;名&gt;</t>
         </is>
       </c>
       <c r="C505" s="1" t="inlineStr">
@@ -16569,7 +16573,7 @@
       </c>
       <c r="D505" s="1" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>自由的；空闲的；免费的</t>
         </is>
       </c>
       <c r="E505" s="1" t="inlineStr">
@@ -16623,7 +16627,7 @@
       </c>
       <c r="B507" s="1" t="inlineStr">
         <is>
-          <t>[võˈta.d͡ʒi] 会&lt;名&gt;</t>
+          <t>[võˈta.d͡ʒi] 意愿；意志；愿望&lt;名&gt;</t>
         </is>
       </c>
       <c r="C507" s="1" t="inlineStr">
@@ -16633,7 +16637,7 @@
       </c>
       <c r="D507" s="1" t="inlineStr">
         <is>
-          <t>会</t>
+          <t>意愿；意志；愿望</t>
         </is>
       </c>
       <c r="E507" s="1" t="inlineStr">
@@ -16911,7 +16915,7 @@
       </c>
       <c r="B516" s="1" t="inlineStr">
         <is>
-          <t>[ĩ.te.ɾeˈsa(ʁ)] 兴趣&lt;动&gt;</t>
+          <t>[ĩ.te.ɾeˈsa(ʁ)] 使感兴趣；感兴趣&lt;动&gt;</t>
         </is>
       </c>
       <c r="C516" s="1" t="inlineStr">
@@ -16921,7 +16925,7 @@
       </c>
       <c r="D516" s="1" t="inlineStr">
         <is>
-          <t>兴趣</t>
+          <t>使感兴趣；感兴趣</t>
         </is>
       </c>
       <c r="E516" s="1" t="inlineStr">
@@ -17103,7 +17107,7 @@
       </c>
       <c r="B522" s="1" t="inlineStr">
         <is>
-          <t>[ˈd͡ʒi.tu] 说&lt;名&gt;</t>
+          <t>[/ˈd͡ʒi.tu/] 所说的；过去分词（dizer）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C522" s="1" t="inlineStr">
@@ -17113,7 +17117,7 @@
       </c>
       <c r="D522" s="1" t="inlineStr">
         <is>
-          <t>说</t>
+          <t>所说的；过去分词（dizer）</t>
         </is>
       </c>
       <c r="E522" s="1" t="inlineStr">
@@ -17359,7 +17363,7 @@
       </c>
       <c r="B530" s="1" t="inlineStr">
         <is>
-          <t>[ˈme.zɐ] 表&lt;名&gt;</t>
+          <t>[ˈme.zɐ] 桌子；餐桌&lt;名&gt;</t>
         </is>
       </c>
       <c r="C530" s="1" t="inlineStr">
@@ -17369,7 +17373,7 @@
       </c>
       <c r="D530" s="1" t="inlineStr">
         <is>
-          <t>表</t>
+          <t>桌子；餐桌</t>
         </is>
       </c>
       <c r="E530" s="1" t="inlineStr">
@@ -17839,7 +17843,7 @@
       </c>
       <c r="B545" s="1" t="inlineStr">
         <is>
-          <t>[ˈɔʁ.dẽj̃] 订单&lt;名&gt;</t>
+          <t>[/ˈɔʁ.dẽj̃/] 秩序；命令；顺序&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C545" s="1" t="inlineStr">
@@ -17849,7 +17853,7 @@
       </c>
       <c r="D545" s="1" t="inlineStr">
         <is>
-          <t>订单</t>
+          <t>秩序；命令；顺序&lt;名&gt;</t>
         </is>
       </c>
       <c r="E545" s="1" t="inlineStr">
@@ -17871,7 +17875,7 @@
       </c>
       <c r="B546" s="1" t="inlineStr">
         <is>
-          <t>[ˈvi.vɐ] 直播&lt;名&gt;</t>
+          <t>[ˈvi.vɐ] 万岁；活着的&lt;名&gt;</t>
         </is>
       </c>
       <c r="C546" s="1" t="inlineStr">
@@ -17881,7 +17885,7 @@
       </c>
       <c r="D546" s="1" t="inlineStr">
         <is>
-          <t>直播</t>
+          <t>万岁；活着的</t>
         </is>
       </c>
       <c r="E546" s="1" t="inlineStr">
@@ -17903,7 +17907,7 @@
       </c>
       <c r="B547" s="1" t="inlineStr">
         <is>
-          <t>[ˈfũ.du] 背景&lt;名&gt;</t>
+          <t>[/ˈfũ.du/] 底部；深处；资金&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C547" s="1" t="inlineStr">
@@ -17913,7 +17917,7 @@
       </c>
       <c r="D547" s="1" t="inlineStr">
         <is>
-          <t>背景</t>
+          <t>底部；深处；资金&lt;名&gt;</t>
         </is>
       </c>
       <c r="E547" s="1" t="inlineStr">
@@ -18095,7 +18099,7 @@
       </c>
       <c r="B553" s="1" t="inlineStr">
         <is>
-          <t>[boˈka.du] 满口的&lt;名&gt;</t>
+          <t>[boˈka.du] 一口；一点儿；块&lt;名&gt;</t>
         </is>
       </c>
       <c r="C553" s="1" t="inlineStr">
@@ -18105,7 +18109,7 @@
       </c>
       <c r="D553" s="1" t="inlineStr">
         <is>
-          <t>满口的</t>
+          <t>一口；一点儿；块</t>
         </is>
       </c>
       <c r="E553" s="1" t="inlineStr">
@@ -18644,7 +18648,7 @@
       </c>
       <c r="C570" s="1" t="inlineStr">
         <is>
-          <t>ler</t>
+          <t>/ler/</t>
         </is>
       </c>
       <c r="D570" s="1" t="inlineStr">
@@ -19151,7 +19155,7 @@
       </c>
       <c r="B586" s="1" t="inlineStr">
         <is>
-          <t>[ˈɐ̃.mu] 阿莫&lt;名&gt;</t>
+          <t>[ˈɐ̃.mu] 主人；东家&lt;名&gt;</t>
         </is>
       </c>
       <c r="C586" s="1" t="inlineStr">
@@ -19161,7 +19165,7 @@
       </c>
       <c r="D586" s="1" t="inlineStr">
         <is>
-          <t>阿莫</t>
+          <t>主人；东家</t>
         </is>
       </c>
       <c r="E586" s="1" t="inlineStr">
@@ -19599,7 +19603,7 @@
       </c>
       <c r="B600" s="1" t="inlineStr">
         <is>
-          <t>[ˈkɐ̃.ma.ɾɐ] 相机&lt;名&gt;</t>
+          <t>[/ˈkɐ̃.ma.ɾɐ/] 房间；议会；室&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C600" s="1" t="inlineStr">
@@ -19609,7 +19613,7 @@
       </c>
       <c r="D600" s="1" t="inlineStr">
         <is>
-          <t>相机</t>
+          <t>房间；议会；室</t>
         </is>
       </c>
       <c r="E600" s="1" t="inlineStr">
@@ -19951,7 +19955,7 @@
       </c>
       <c r="B611" s="1" t="inlineStr">
         <is>
-          <t>[ʃaˈma.du] 被称为&lt;名&gt;</t>
+          <t>[/ʃaˈma.du/] 呼叫；呼唤&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C611" s="1" t="inlineStr">
@@ -19961,7 +19965,7 @@
       </c>
       <c r="D611" s="1" t="inlineStr">
         <is>
-          <t>被称为</t>
+          <t>呼叫；呼唤&lt;名&gt;</t>
         </is>
       </c>
       <c r="E611" s="1" t="inlineStr">
@@ -20559,7 +20563,7 @@
       </c>
       <c r="B630" s="1" t="inlineStr">
         <is>
-          <t>[ˈte.ɾis] 特雷斯&lt;名&gt;</t>
+          <t>[ˈte.ɾis] 有；拥有&lt;名&gt;</t>
         </is>
       </c>
       <c r="C630" s="1" t="inlineStr">
@@ -20569,7 +20573,7 @@
       </c>
       <c r="D630" s="1" t="inlineStr">
         <is>
-          <t>特雷斯</t>
+          <t>有；拥有</t>
         </is>
       </c>
       <c r="E630" s="1" t="inlineStr">
@@ -20596,7 +20600,7 @@
       </c>
       <c r="C631" s="1" t="inlineStr">
         <is>
-          <t>ˈnãʊ̃</t>
+          <t>/ˈnãʊ̃/</t>
         </is>
       </c>
       <c r="D631" s="1" t="inlineStr">
@@ -20719,7 +20723,7 @@
       </c>
       <c r="B635" s="1" t="inlineStr">
         <is>
-          <t>[beˈbi.dɐ] 喝&lt;名&gt;</t>
+          <t>[beˈbi.dɐ] 饮料；酒&lt;名&gt;</t>
         </is>
       </c>
       <c r="C635" s="1" t="inlineStr">
@@ -20729,7 +20733,7 @@
       </c>
       <c r="D635" s="1" t="inlineStr">
         <is>
-          <t>喝</t>
+          <t>饮料；酒</t>
         </is>
       </c>
       <c r="E635" s="1" t="inlineStr">
@@ -20783,7 +20787,7 @@
       </c>
       <c r="B637" s="1" t="inlineStr">
         <is>
-          <t>[ˈba.zi] 基地&lt;名&gt;</t>
+          <t>[/ˈba.zi/] 基础；基地&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C637" s="1" t="inlineStr">
@@ -20793,7 +20797,7 @@
       </c>
       <c r="D637" s="1" t="inlineStr">
         <is>
-          <t>基地</t>
+          <t>基础；基地&lt;名&gt;</t>
         </is>
       </c>
       <c r="E637" s="1" t="inlineStr">
@@ -21167,7 +21171,7 @@
       </c>
       <c r="B649" s="1" t="inlineStr">
         <is>
-          <t>[a.seʁˈka(ʁ)] 方法&lt;动&gt;</t>
+          <t>[a.seʁˈka(ʁ)] 靠近；接近&lt;动&gt;</t>
         </is>
       </c>
       <c r="C649" s="1" t="inlineStr">
@@ -21177,7 +21181,7 @@
       </c>
       <c r="D649" s="1" t="inlineStr">
         <is>
-          <t>方法</t>
+          <t>靠近；接近</t>
         </is>
       </c>
       <c r="E649" s="1" t="inlineStr">
@@ -21199,7 +21203,7 @@
       </c>
       <c r="B650" s="1" t="inlineStr">
         <is>
-          <t>[kaˈi(ʁ)] 秋天&lt;动&gt;</t>
+          <t>[kaˈi(ʁ)] 落下；跌落；倒下&lt;动&gt;</t>
         </is>
       </c>
       <c r="C650" s="1" t="inlineStr">
@@ -21209,7 +21213,7 @@
       </c>
       <c r="D650" s="1" t="inlineStr">
         <is>
-          <t>秋天</t>
+          <t>落下；跌落；倒下</t>
         </is>
       </c>
       <c r="E650" s="1" t="inlineStr">
@@ -21295,7 +21299,7 @@
       </c>
       <c r="B653" s="1" t="inlineStr">
         <is>
-          <t>[mẽˈt͡ʃi(ʁ)] 谎言&lt;动&gt;</t>
+          <t>[mẽˈt͡ʃi(ʁ)] 说谎；撒谎&lt;动&gt;</t>
         </is>
       </c>
       <c r="C653" s="1" t="inlineStr">
@@ -21305,7 +21309,7 @@
       </c>
       <c r="D653" s="1" t="inlineStr">
         <is>
-          <t>谎言</t>
+          <t>说谎；撒谎</t>
         </is>
       </c>
       <c r="E653" s="1" t="inlineStr">
@@ -21327,7 +21331,7 @@
       </c>
       <c r="B654" s="1" t="inlineStr">
         <is>
-          <t>[ˈkɔs.tɐs] 回来&lt;名&gt;</t>
+          <t>[ˈkɔs.tɐs] 背；背部&lt;名&gt;</t>
         </is>
       </c>
       <c r="C654" s="1" t="inlineStr">
@@ -21337,7 +21341,7 @@
       </c>
       <c r="D654" s="1" t="inlineStr">
         <is>
-          <t>回来</t>
+          <t>背；背部</t>
         </is>
       </c>
       <c r="E654" s="1" t="inlineStr">
@@ -21519,7 +21523,7 @@
       </c>
       <c r="B660" s="1" t="inlineStr">
         <is>
-          <t>[ˈoj.tu] 八&lt;名&gt;</t>
+          <t>[/ˈoj.tu/] 八&lt;数&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C660" s="1" t="inlineStr">
@@ -21529,7 +21533,7 @@
       </c>
       <c r="D660" s="1" t="inlineStr">
         <is>
-          <t>八</t>
+          <t>八&lt;数&gt;</t>
         </is>
       </c>
       <c r="E660" s="1" t="inlineStr">
@@ -22415,7 +22419,7 @@
       </c>
       <c r="B688" s="1" t="inlineStr">
         <is>
-          <t>[saˈi.dɐ] 退出&lt;名&gt;</t>
+          <t>[/saˈi.dɐ/] 出口；离开&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C688" s="1" t="inlineStr">
@@ -22425,7 +22429,7 @@
       </c>
       <c r="D688" s="1" t="inlineStr">
         <is>
-          <t>退出</t>
+          <t>出口；离开</t>
         </is>
       </c>
       <c r="E688" s="1" t="inlineStr">
@@ -22479,7 +22483,7 @@
       </c>
       <c r="B690" s="1" t="inlineStr">
         <is>
-          <t>[is.pliˈka(ʁ)] 解释一下&lt;动&gt;</t>
+          <t>[/is.pliˈka(ʁ)/] 解释&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C690" s="1" t="inlineStr">
@@ -22489,7 +22493,7 @@
       </c>
       <c r="D690" s="1" t="inlineStr">
         <is>
-          <t>解释一下</t>
+          <t>解释</t>
         </is>
       </c>
       <c r="E690" s="1" t="inlineStr">
@@ -22706,7 +22710,11 @@
           <t>侦探&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C697" s="1" t="inlineStr"/>
+      <c r="C697" s="1" t="inlineStr">
+        <is>
+          <t>/de.teˈt͡ʃi.vi/</t>
+        </is>
+      </c>
       <c r="D697" s="1" t="inlineStr">
         <is>
           <t>侦探</t>
@@ -22731,7 +22739,7 @@
       </c>
       <c r="B698" s="1" t="inlineStr">
         <is>
-          <t>[ˈo(w).ɾus] 钻石&lt;名&gt;</t>
+          <t>[ˈo(w).ɾus] 金；黄金；（纸牌）方块&lt;名&gt;</t>
         </is>
       </c>
       <c r="C698" s="1" t="inlineStr">
@@ -22741,7 +22749,7 @@
       </c>
       <c r="D698" s="1" t="inlineStr">
         <is>
-          <t>钻石</t>
+          <t>金；黄金；（纸牌）方块</t>
         </is>
       </c>
       <c r="E698" s="1" t="inlineStr">
@@ -23243,7 +23251,7 @@
       </c>
       <c r="B714" s="1" t="inlineStr">
         <is>
-          <t>[liˈda(ʁ)] 交易&lt;动&gt;</t>
+          <t>[liˈda(ʁ)] 处理；对付；打交道&lt;动&gt;</t>
         </is>
       </c>
       <c r="C714" s="1" t="inlineStr">
@@ -23253,7 +23261,7 @@
       </c>
       <c r="D714" s="1" t="inlineStr">
         <is>
-          <t>交易</t>
+          <t>处理；对付；打交道</t>
         </is>
       </c>
       <c r="E714" s="1" t="inlineStr">
@@ -23280,7 +23288,7 @@
       </c>
       <c r="C715" s="1" t="inlineStr">
         <is>
-          <t>ˈxɛ.gɾəs</t>
+          <t>/ˈxɛ.gɾəs/</t>
         </is>
       </c>
       <c r="D715" s="1" t="inlineStr">
@@ -23627,7 +23635,7 @@
       </c>
       <c r="B726" s="1" t="inlineStr">
         <is>
-          <t>[d͡ʒiˈɾej.tɐ] 对&lt;名&gt;</t>
+          <t>[d͡ʒiˈɾej.tɐ] 右；右边&lt;名&gt;</t>
         </is>
       </c>
       <c r="C726" s="1" t="inlineStr">
@@ -23637,7 +23645,7 @@
       </c>
       <c r="D726" s="1" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>右；右边</t>
         </is>
       </c>
       <c r="E726" s="1" t="inlineStr">
@@ -24459,7 +24467,7 @@
       </c>
       <c r="B752" s="1" t="inlineStr">
         <is>
-          <t>[paˈuw] 保罗&lt;名&gt;</t>
+          <t>[/paˈuw/] 木桩&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C752" s="1" t="inlineStr">
@@ -24469,7 +24477,7 @@
       </c>
       <c r="D752" s="1" t="inlineStr">
         <is>
-          <t>保罗</t>
+          <t>木桩&lt;名&gt;</t>
         </is>
       </c>
       <c r="E752" s="1" t="inlineStr">
@@ -26219,7 +26227,7 @@
       </c>
       <c r="B807" s="1" t="inlineStr">
         <is>
-          <t>[ˈmõ.t͡ʃi] 安装&lt;名&gt;</t>
+          <t>[ˈmõ.t͡ʃi] 堆；一堆；山丘&lt;名&gt;</t>
         </is>
       </c>
       <c r="C807" s="1" t="inlineStr">
@@ -26229,7 +26237,7 @@
       </c>
       <c r="D807" s="1" t="inlineStr">
         <is>
-          <t>安装</t>
+          <t>堆；一堆；山丘</t>
         </is>
       </c>
       <c r="E807" s="1" t="inlineStr">
@@ -26859,7 +26867,7 @@
       </c>
       <c r="B827" s="1" t="inlineStr">
         <is>
-          <t>[peʁˈse.bi] 意识到&lt;名&gt;</t>
+          <t>[/peʁˈse.bi/] perceber 的变位（第三人称单数）；原形意为 意识到&lt;动&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C827" s="1" t="inlineStr">
@@ -26869,7 +26877,7 @@
       </c>
       <c r="D827" s="1" t="inlineStr">
         <is>
-          <t>意识到</t>
+          <t>perceber 的变位（第三人称单数）；原形意为 意识到&lt;动&gt;</t>
         </is>
       </c>
       <c r="E827" s="1" t="inlineStr">
@@ -27243,7 +27251,7 @@
       </c>
       <c r="B839" s="1" t="inlineStr">
         <is>
-          <t>[d͡ʒiˈa.bus] 地狱&lt;叹&gt;</t>
+          <t>[d͡ʒiˈa.bus] 魔鬼；恶魔；见鬼&lt;叹&gt;</t>
         </is>
       </c>
       <c r="C839" s="1" t="inlineStr">
@@ -27253,7 +27261,7 @@
       </c>
       <c r="D839" s="1" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>魔鬼；恶魔；见鬼</t>
         </is>
       </c>
       <c r="E839" s="1" t="inlineStr">
@@ -28299,7 +28307,7 @@
       </c>
       <c r="B872" s="1" t="inlineStr">
         <is>
-          <t>[ˈi.du] 消失了&lt;名&gt;</t>
+          <t>[ˈi.du] 去了的；已去的&lt;名&gt;</t>
         </is>
       </c>
       <c r="C872" s="1" t="inlineStr">
@@ -28309,7 +28317,7 @@
       </c>
       <c r="D872" s="1" t="inlineStr">
         <is>
-          <t>消失了</t>
+          <t>去了的；已去的</t>
         </is>
       </c>
       <c r="E872" s="1" t="inlineStr">
@@ -28464,7 +28472,7 @@
       </c>
       <c r="C877" s="1" t="inlineStr">
         <is>
-          <t>ˈtɾas</t>
+          <t>/ˈtɾas/</t>
         </is>
       </c>
       <c r="D877" s="1" t="inlineStr">
@@ -28555,7 +28563,7 @@
       </c>
       <c r="B880" s="1" t="inlineStr">
         <is>
-          <t>[ˈbɔ.bi] 鲍勃&lt;名&gt;</t>
+          <t>[ˈbɔ.bi] 傻的；愚蠢的；波波头&lt;名&gt;</t>
         </is>
       </c>
       <c r="C880" s="1" t="inlineStr">
@@ -28565,7 +28573,7 @@
       </c>
       <c r="D880" s="1" t="inlineStr">
         <is>
-          <t>鲍勃</t>
+          <t>傻的；愚蠢的；波波头</t>
         </is>
       </c>
       <c r="E880" s="1" t="inlineStr">
@@ -28683,7 +28691,7 @@
       </c>
       <c r="B884" s="1" t="inlineStr">
         <is>
-          <t>[lĩˈpa(ʁ)] 干净&lt;动&gt;</t>
+          <t>[lĩˈpa(ʁ)] 打扫；清洗；清洁&lt;动&gt;</t>
         </is>
       </c>
       <c r="C884" s="1" t="inlineStr">
@@ -28693,7 +28701,7 @@
       </c>
       <c r="D884" s="1" t="inlineStr">
         <is>
-          <t>干净</t>
+          <t>打扫；清洗；清洁</t>
         </is>
       </c>
       <c r="E884" s="1" t="inlineStr">
@@ -29008,7 +29016,7 @@
       </c>
       <c r="C894" s="1" t="inlineStr">
         <is>
-          <t>dʒi.ɾe.ˈsãʊ̃</t>
+          <t>/dʒi.ɾe.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D894" s="1" t="inlineStr">
@@ -29195,7 +29203,7 @@
       </c>
       <c r="B900" s="1" t="inlineStr">
         <is>
-          <t>[ˈlɛ.vi] 光&lt;形&gt;</t>
+          <t>[ˈlɛ.vi] 轻的；轻微的；清淡的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C900" s="1" t="inlineStr">
@@ -29205,7 +29213,7 @@
       </c>
       <c r="D900" s="1" t="inlineStr">
         <is>
-          <t>光</t>
+          <t>轻的；轻微的；清淡的</t>
         </is>
       </c>
       <c r="E900" s="1" t="inlineStr">
@@ -29392,7 +29400,7 @@
       </c>
       <c r="C906" s="1" t="inlineStr">
         <is>
-          <t>hei</t>
+          <t>/hei/</t>
         </is>
       </c>
       <c r="D906" s="1" t="inlineStr">
@@ -29867,7 +29875,7 @@
       </c>
       <c r="B921" s="1" t="inlineStr">
         <is>
-          <t>[ˈpɾɛs.t͡ʃis] 关于&lt;形&gt;</t>
+          <t>[ˈpɾɛs.t͡ʃis] 即将；快要&lt;形&gt;</t>
         </is>
       </c>
       <c r="C921" s="1" t="inlineStr">
@@ -29877,7 +29885,7 @@
       </c>
       <c r="D921" s="1" t="inlineStr">
         <is>
-          <t>关于</t>
+          <t>即将；快要</t>
         </is>
       </c>
       <c r="E921" s="1" t="inlineStr">
@@ -29963,7 +29971,7 @@
       </c>
       <c r="B924" s="1" t="inlineStr">
         <is>
-          <t>[ĩˈte(j).ɾu] 整体&lt;名&gt;</t>
+          <t>[/ĩˈte(j).ɾu/] 完整的&lt;形&gt;；整个的&lt;形&gt;（“整数”为 número inteiro）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C924" s="1" t="inlineStr">
@@ -29973,7 +29981,7 @@
       </c>
       <c r="D924" s="1" t="inlineStr">
         <is>
-          <t>整体</t>
+          <t>完整的&lt;形&gt;；整个的&lt;形&gt;（“整数”为 número inteiro）</t>
         </is>
       </c>
       <c r="E924" s="1" t="inlineStr">
@@ -29995,7 +30003,7 @@
       </c>
       <c r="B925" s="1" t="inlineStr">
         <is>
-          <t>[ˈbɾɐ̃.kɐ] 白色&lt;名&gt;</t>
+          <t>[/ˈbɾɐ̃.kɐ/] 白色的&lt;形&gt;（branco 的阴性形式）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C925" s="1" t="inlineStr">
@@ -30005,7 +30013,7 @@
       </c>
       <c r="D925" s="1" t="inlineStr">
         <is>
-          <t>白色</t>
+          <t>白色的&lt;形&gt;（branco 的阴性形式）</t>
         </is>
       </c>
       <c r="E925" s="1" t="inlineStr">
@@ -30571,7 +30579,7 @@
       </c>
       <c r="B943" s="1" t="inlineStr">
         <is>
-          <t>[ˈvi.ɾɐ̃w̃] 锯&lt;动&gt;</t>
+          <t>[ˈvi.ɾɐ̃w̃] 看见；看到；转动&lt;动&gt;</t>
         </is>
       </c>
       <c r="C943" s="1" t="inlineStr">
@@ -30581,7 +30589,7 @@
       </c>
       <c r="D943" s="1" t="inlineStr">
         <is>
-          <t>锯</t>
+          <t>看见；看到；转动</t>
         </is>
       </c>
       <c r="E943" s="1" t="inlineStr">
@@ -30832,7 +30840,7 @@
       </c>
       <c r="C951" s="1" t="inlineStr">
         <is>
-          <t>a.ʒu.ˈda.lʊ</t>
+          <t>/a.ʒu.ˈda.lʊ/</t>
         </is>
       </c>
       <c r="D951" s="1" t="inlineStr">
@@ -31307,7 +31315,7 @@
       </c>
       <c r="B966" s="1" t="inlineStr">
         <is>
-          <t>[a.me.ɾiˈkɐ̃.nu] 美国&lt;名&gt;</t>
+          <t>[a.me.ɾiˈkɐ̃.nu] 美国的；美国人；美洲的&lt;名&gt;</t>
         </is>
       </c>
       <c r="C966" s="1" t="inlineStr">
@@ -31317,7 +31325,7 @@
       </c>
       <c r="D966" s="1" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>美国的；美国人；美洲的</t>
         </is>
       </c>
       <c r="E966" s="1" t="inlineStr">
@@ -31504,7 +31512,7 @@
       </c>
       <c r="C972" s="1" t="inlineStr">
         <is>
-          <t>a.ˈsãʊ̃</t>
+          <t>/a.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D972" s="1" t="inlineStr">
@@ -32144,7 +32152,7 @@
       </c>
       <c r="C992" s="1" t="inlineStr">
         <is>
-          <t>ẽ.kõ.ˈtɾa.ɾãʊ̃</t>
+          <t>/ẽ.kõ.ˈtɾa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D992" s="1" t="inlineStr">
@@ -32336,7 +32344,7 @@
       </c>
       <c r="C998" s="1" t="inlineStr">
         <is>
-          <t>e.ˈsep.tʊ</t>
+          <t>/e.ˈsep.tʊ/</t>
         </is>
       </c>
       <c r="D998" s="1" t="inlineStr">
@@ -32715,17 +32723,17 @@
       </c>
       <c r="B1010" s="1" t="inlineStr">
         <is>
-          <t>[es.pe.ˈta.ku.lʊ] 显示&lt;名&gt;</t>
+          <t>[es.pe.ˈta.ku.lʊ] 演出；表演；壮观场面&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1010" s="1" t="inlineStr">
         <is>
-          <t>es.pe.ˈta.ku.lʊ</t>
+          <t>/es.pe.ˈta.ku.lʊ/</t>
         </is>
       </c>
       <c r="D1010" s="1" t="inlineStr">
         <is>
-          <t>显示</t>
+          <t>演出；表演；壮观场面</t>
         </is>
       </c>
       <c r="E1010" s="1" t="inlineStr">
@@ -33419,7 +33427,7 @@
       </c>
       <c r="B1032" s="1" t="inlineStr">
         <is>
-          <t>[ˈmaw.tɐ] 马耳他&lt;名&gt;</t>
+          <t>[ˈmaw.tɐ] 一群人；大伙儿；伙伴们&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1032" s="1" t="inlineStr">
@@ -33429,7 +33437,7 @@
       </c>
       <c r="D1032" s="1" t="inlineStr">
         <is>
-          <t>马耳他</t>
+          <t>一群人；大伙儿；伙伴们</t>
         </is>
       </c>
       <c r="E1032" s="1" t="inlineStr">
@@ -33515,7 +33523,7 @@
       </c>
       <c r="B1035" s="1" t="inlineStr">
         <is>
-          <t>[ʒuw.ɡaˈmẽ.tu] 判断力&lt;名&gt;</t>
+          <t>[/ʒuw.ɡaˈmẽ.tu/] 判断；审判&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1035" s="1" t="inlineStr">
@@ -33525,7 +33533,7 @@
       </c>
       <c r="D1035" s="1" t="inlineStr">
         <is>
-          <t>判断力</t>
+          <t>判断；审判&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1035" s="1" t="inlineStr">
@@ -33643,7 +33651,7 @@
       </c>
       <c r="B1039" s="1" t="inlineStr">
         <is>
-          <t>[ˈpɾe.tu] 黑色&lt;名&gt;</t>
+          <t>[/ˈpɾe.tu/] 黑色的&lt;形&gt;；黑色&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1039" s="1" t="inlineStr">
@@ -33653,7 +33661,7 @@
       </c>
       <c r="D1039" s="1" t="inlineStr">
         <is>
-          <t>黑色</t>
+          <t>黑色的&lt;形&gt;；黑色&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1039" s="1" t="inlineStr">
@@ -33771,7 +33779,7 @@
       </c>
       <c r="B1043" s="1" t="inlineStr">
         <is>
-          <t>[paʁˈt͡ʃi.du] 聚会&lt;名&gt;</t>
+          <t>[paʁˈt͡ʃi.du] 政党；党派&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1043" s="1" t="inlineStr">
@@ -33781,7 +33789,7 @@
       </c>
       <c r="D1043" s="1" t="inlineStr">
         <is>
-          <t>聚会</t>
+          <t>政党；党派</t>
         </is>
       </c>
       <c r="E1043" s="1" t="inlineStr">
@@ -34091,7 +34099,7 @@
       </c>
       <c r="B1053" s="1" t="inlineStr">
         <is>
-          <t>[koˈʁi.dɐ] 种族&lt;名&gt;</t>
+          <t>[koˈʁi.dɐ] 赛跑；奔跑；疾驰&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1053" s="1" t="inlineStr">
@@ -34101,7 +34109,7 @@
       </c>
       <c r="D1053" s="1" t="inlineStr">
         <is>
-          <t>种族</t>
+          <t>赛跑；奔跑；疾驰</t>
         </is>
       </c>
       <c r="E1053" s="1" t="inlineStr">
@@ -34123,7 +34131,7 @@
       </c>
       <c r="B1054" s="1" t="inlineStr">
         <is>
-          <t>[de(j)ˈʃa.du] 左&lt;形&gt;</t>
+          <t>[de(j)ˈʃa.du] 留下的；剩下的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C1054" s="1" t="inlineStr">
@@ -34133,7 +34141,7 @@
       </c>
       <c r="D1054" s="1" t="inlineStr">
         <is>
-          <t>左</t>
+          <t>留下的；剩下的</t>
         </is>
       </c>
       <c r="E1054" s="1" t="inlineStr">
@@ -34224,7 +34232,7 @@
       </c>
       <c r="C1057" s="1" t="inlineStr">
         <is>
-          <t>/pɛʁˈdɐ̃w̃/ [pɛɦˈdɐ̃ʊ̯̃]</t>
+          <t>/pɛʁˈdɐ̃w̃/</t>
         </is>
       </c>
       <c r="D1057" s="1" t="inlineStr">
@@ -34512,7 +34520,7 @@
       </c>
       <c r="C1066" s="1" t="inlineStr">
         <is>
-          <t>ko.ˈxɛ.tʊ</t>
+          <t>/ko.ˈxɛ.tʊ/</t>
         </is>
       </c>
       <c r="D1066" s="1" t="inlineStr">
@@ -34539,7 +34547,7 @@
       </c>
       <c r="B1067" s="1" t="inlineStr">
         <is>
-          <t>[liˈɡa.du] 上&lt;形&gt;</t>
+          <t>[liˈɡa.du] 连接的；开着的；接通的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C1067" s="1" t="inlineStr">
@@ -34549,7 +34557,7 @@
       </c>
       <c r="D1067" s="1" t="inlineStr">
         <is>
-          <t>上</t>
+          <t>连接的；开着的；接通的</t>
         </is>
       </c>
       <c r="E1067" s="1" t="inlineStr">
@@ -34763,7 +34771,7 @@
       </c>
       <c r="B1074" s="1" t="inlineStr">
         <is>
-          <t>[ˈveʁ.d͡ʒi] 绿色&lt;名&gt;</t>
+          <t>[/ˈveʁ.d͡ʒi/] 绿色的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1074" s="1" t="inlineStr">
@@ -34773,7 +34781,7 @@
       </c>
       <c r="D1074" s="1" t="inlineStr">
         <is>
-          <t>绿色</t>
+          <t>绿色的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1074" s="1" t="inlineStr">
@@ -34960,7 +34968,7 @@
       </c>
       <c r="C1080" s="1" t="inlineStr">
         <is>
-          <t>dʒi.ɾe.ˈtox</t>
+          <t>/dʒi.ɾe.ˈtox/</t>
         </is>
       </c>
       <c r="D1080" s="1" t="inlineStr">
@@ -35595,7 +35603,7 @@
       </c>
       <c r="B1100" s="1" t="inlineStr">
         <is>
-          <t>[ʁiˈd͡ʒi.ku.lu] 可笑&lt;名&gt;</t>
+          <t>[/ʁiˈd͡ʒi.ku.lu/] 可笑的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1100" s="1" t="inlineStr">
@@ -35605,7 +35613,7 @@
       </c>
       <c r="D1100" s="1" t="inlineStr">
         <is>
-          <t>可笑</t>
+          <t>可笑的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1100" s="1" t="inlineStr">
@@ -36203,7 +36211,7 @@
       </c>
       <c r="B1119" s="1" t="inlineStr">
         <is>
-          <t>[ˈpos.tu] 帖子&lt;名&gt;</t>
+          <t>[ˈpos.tu] 放置的；位置；岗位；站&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1119" s="1" t="inlineStr">
@@ -36213,7 +36221,7 @@
       </c>
       <c r="D1119" s="1" t="inlineStr">
         <is>
-          <t>帖子</t>
+          <t>放置的；位置；岗位；站</t>
         </is>
       </c>
       <c r="E1119" s="1" t="inlineStr">
@@ -37355,7 +37363,7 @@
       </c>
       <c r="B1155" s="1" t="inlineStr">
         <is>
-          <t>[isˈku.ɾu] 黑暗&lt;名&gt;</t>
+          <t>[/isˈku.ɾu/] 黑暗的&lt;形&gt;；深色的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1155" s="1" t="inlineStr">
@@ -37365,7 +37373,7 @@
       </c>
       <c r="D1155" s="1" t="inlineStr">
         <is>
-          <t>黑暗</t>
+          <t>黑暗的&lt;形&gt;；深色的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1155" s="1" t="inlineStr">
@@ -37419,7 +37427,7 @@
       </c>
       <c r="B1157" s="1" t="inlineStr">
         <is>
-          <t>[le.vɐ̃ˈta(ʁ)] 电梯&lt;动&gt;</t>
+          <t>[le.vɐ̃ˈta(ʁ)] 举起；抬起；起床&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1157" s="1" t="inlineStr">
@@ -37429,7 +37437,7 @@
       </c>
       <c r="D1157" s="1" t="inlineStr">
         <is>
-          <t>电梯</t>
+          <t>举起；抬起；起床</t>
         </is>
       </c>
       <c r="E1157" s="1" t="inlineStr">
@@ -37515,7 +37523,7 @@
       </c>
       <c r="B1160" s="1" t="inlineStr">
         <is>
-          <t>[ĩˈpɾẽ.sɐ] 按&lt;名&gt;</t>
+          <t>[ĩˈpɾẽ.sɐ] 新闻界；报刊；出版社&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1160" s="1" t="inlineStr">
@@ -37525,7 +37533,7 @@
       </c>
       <c r="D1160" s="1" t="inlineStr">
         <is>
-          <t>按</t>
+          <t>新闻界；报刊；出版社</t>
         </is>
       </c>
       <c r="E1160" s="1" t="inlineStr">
@@ -38315,17 +38323,17 @@
       </c>
       <c r="B1185" s="1" t="inlineStr">
         <is>
-          <t>[po.li.ˈsi.ə] 警察&lt;名&gt;</t>
+          <t>[po.li.ˈsi.ə] policia 是动词（policiar 的变位，“巡逻/维持治安”）；“警察”应为 polícia&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1185" s="1" t="inlineStr">
         <is>
-          <t>po.li.ˈsi.ə</t>
+          <t>/po.li.ˈsi.ə/</t>
         </is>
       </c>
       <c r="D1185" s="1" t="inlineStr">
         <is>
-          <t>警察</t>
+          <t>policia 是动词（policiar 的变位，“巡逻/维持治安”）；“警察”应为 polícia&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1185" s="1" t="inlineStr">
@@ -38960,7 +38968,7 @@
       </c>
       <c r="C1205" s="1" t="inlineStr">
         <is>
-          <t>e.ˈksa.tʊ</t>
+          <t>/e.ˈksa.tʊ/</t>
         </is>
       </c>
       <c r="D1205" s="1" t="inlineStr">
@@ -39502,10 +39510,14 @@
           <t>先生&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1222" s="1" t="inlineStr"/>
+      <c r="C1222" s="1" t="inlineStr">
+        <is>
+          <t>/sɝː/</t>
+        </is>
+      </c>
       <c r="D1222" s="1" t="inlineStr">
         <is>
-          <t>先生</t>
+          <t>（英语）先生；爵士（非葡萄牙语词汇）</t>
         </is>
       </c>
       <c r="E1222" s="1" t="inlineStr">
@@ -39628,7 +39640,7 @@
       </c>
       <c r="C1226" s="1" t="inlineStr">
         <is>
-          <t>ʃe.ˈga.ɾãʊ̃</t>
+          <t>/ʃe.ˈga.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1226" s="1" t="inlineStr">
@@ -39655,7 +39667,7 @@
       </c>
       <c r="B1227" s="1" t="inlineStr">
         <is>
-          <t>[ˈbaj.li] 跳舞&lt;名&gt;</t>
+          <t>[ˈbaj.li] 舞会&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1227" s="1" t="inlineStr">
@@ -39665,7 +39677,7 @@
       </c>
       <c r="D1227" s="1" t="inlineStr">
         <is>
-          <t>跳舞</t>
+          <t>舞会</t>
         </is>
       </c>
       <c r="E1227" s="1" t="inlineStr">
@@ -39847,7 +39859,7 @@
       </c>
       <c r="B1233" s="1" t="inlineStr">
         <is>
-          <t>[a.pɾe.zẽˈta(ʁ)] 现在&lt;动&gt;</t>
+          <t>[a.pɾe.zẽˈta(ʁ)] 介绍；展示；提交&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1233" s="1" t="inlineStr">
@@ -39857,7 +39869,7 @@
       </c>
       <c r="D1233" s="1" t="inlineStr">
         <is>
-          <t>现在</t>
+          <t>介绍；展示；提交</t>
         </is>
       </c>
       <c r="E1233" s="1" t="inlineStr">
@@ -39879,7 +39891,7 @@
       </c>
       <c r="B1234" s="1" t="inlineStr">
         <is>
-          <t>[liˈʃa(ʁ)] 沙子&lt;动&gt;</t>
+          <t>[liˈʃa(ʁ)] 打磨；用砂纸磨光&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1234" s="1" t="inlineStr">
@@ -39889,7 +39901,7 @@
       </c>
       <c r="D1234" s="1" t="inlineStr">
         <is>
-          <t>沙子</t>
+          <t>打磨；用砂纸磨光</t>
         </is>
       </c>
       <c r="E1234" s="1" t="inlineStr">
@@ -39943,17 +39955,17 @@
       </c>
       <c r="B1236" s="1" t="inlineStr">
         <is>
-          <t>[ˈa ˈɛ.li] 阿尔&lt;名&gt;</t>
+          <t>[/ˈaw/] 铝（alumínio 的缩写）&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1236" s="1" t="inlineStr">
         <is>
-          <t>/ˈa ˈɛ.li/</t>
+          <t>/ˈaw/</t>
         </is>
       </c>
       <c r="D1236" s="1" t="inlineStr">
         <is>
-          <t>阿尔</t>
+          <t>铝（alumínio 的缩写）&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1236" s="1" t="inlineStr">
@@ -41223,7 +41235,7 @@
       </c>
       <c r="B1276" s="1" t="inlineStr">
         <is>
-          <t>[ˈku] 屁股&lt;名&gt;</t>
+          <t>[/ˈku/] 肛门&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1276" s="1" t="inlineStr">
@@ -41233,7 +41245,7 @@
       </c>
       <c r="D1276" s="1" t="inlineStr">
         <is>
-          <t>屁股</t>
+          <t>肛门&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1276" s="1" t="inlineStr">
@@ -41356,7 +41368,7 @@
       </c>
       <c r="C1280" s="1" t="inlineStr">
         <is>
-          <t>pɾo.ˈʒɛ.tʊ</t>
+          <t>/pɾo.ˈʒɛ.tʊ/</t>
         </is>
       </c>
       <c r="D1280" s="1" t="inlineStr">
@@ -41580,7 +41592,7 @@
       </c>
       <c r="C1287" s="1" t="inlineStr">
         <is>
-          <t>ob.ʒe.ˈtʃi.vʊ</t>
+          <t>/ob.ʒe.ˈtʃi.vʊ/</t>
         </is>
       </c>
       <c r="D1287" s="1" t="inlineStr">
@@ -42183,7 +42195,7 @@
       </c>
       <c r="B1306" s="1" t="inlineStr">
         <is>
-          <t>[ʃe(j)ˈɾa(ʁ)] 气味&lt;动&gt;</t>
+          <t>[ʃe(j)ˈɾa(ʁ)] 闻；嗅；发出气味&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1306" s="1" t="inlineStr">
@@ -42193,7 +42205,7 @@
       </c>
       <c r="D1306" s="1" t="inlineStr">
         <is>
-          <t>气味</t>
+          <t>闻；嗅；发出气味</t>
         </is>
       </c>
       <c r="E1306" s="1" t="inlineStr">
@@ -42407,7 +42419,7 @@
       </c>
       <c r="B1313" s="1" t="inlineStr">
         <is>
-          <t>[ˈʒi.ɾu] 旋转&lt;名&gt;</t>
+          <t>[/ˈʒi.ɾu/] 可爱的；旋转&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1313" s="1" t="inlineStr">
@@ -42417,7 +42429,7 @@
       </c>
       <c r="D1313" s="1" t="inlineStr">
         <is>
-          <t>旋转</t>
+          <t>可爱的；旋转</t>
         </is>
       </c>
       <c r="E1313" s="1" t="inlineStr">
@@ -42732,7 +42744,7 @@
       </c>
       <c r="C1323" s="1" t="inlineStr">
         <is>
-          <t>pɾo.te.ˈsãʊ̃</t>
+          <t>/pɾo.te.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D1323" s="1" t="inlineStr">
@@ -43052,7 +43064,7 @@
       </c>
       <c r="C1333" s="1" t="inlineStr">
         <is>
-          <t>ˈxõ.mə</t>
+          <t>/ˈxõ.mə/</t>
         </is>
       </c>
       <c r="D1333" s="1" t="inlineStr">
@@ -43271,7 +43283,7 @@
       </c>
       <c r="B1340" s="1" t="inlineStr">
         <is>
-          <t>[vaˈzi.u] 空的&lt;名&gt;</t>
+          <t>[/vaˈzi.u/] 空的；空虚&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1340" s="1" t="inlineStr">
@@ -43281,7 +43293,7 @@
       </c>
       <c r="D1340" s="1" t="inlineStr">
         <is>
-          <t>空的</t>
+          <t>空的；空虚&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1340" s="1" t="inlineStr">
@@ -43399,7 +43411,7 @@
       </c>
       <c r="B1344" s="1" t="inlineStr">
         <is>
-          <t>[ĩ.pɾeˈsɐ̃w̃] 印刷&lt;名&gt;</t>
+          <t>[/ĩ.pɾeˈsɐ̃w̃/] 印象；印刷&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1344" s="1" t="inlineStr">
@@ -43409,7 +43421,7 @@
       </c>
       <c r="D1344" s="1" t="inlineStr">
         <is>
-          <t>印刷</t>
+          <t>印象；印刷&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1344" s="1" t="inlineStr">
@@ -43527,7 +43539,7 @@
       </c>
       <c r="B1348" s="1" t="inlineStr">
         <is>
-          <t>[ẽ.fɾẽˈta(ʁ)] 脸&lt;动&gt;</t>
+          <t>[ẽ.fɾẽˈta(ʁ)] 面对；对抗&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1348" s="1" t="inlineStr">
@@ -43537,7 +43549,7 @@
       </c>
       <c r="D1348" s="1" t="inlineStr">
         <is>
-          <t>脸</t>
+          <t>面对；对抗</t>
         </is>
       </c>
       <c r="E1348" s="1" t="inlineStr">
@@ -43818,7 +43830,11 @@
           <t>废话&lt;动&gt;</t>
         </is>
       </c>
-      <c r="C1357" s="1" t="inlineStr"/>
+      <c r="C1357" s="1" t="inlineStr">
+        <is>
+          <t>/tɾeˈta(ʁ)/</t>
+        </is>
+      </c>
       <c r="D1357" s="1" t="inlineStr">
         <is>
           <t>废话</t>
@@ -43976,7 +43992,7 @@
       </c>
       <c r="C1362" s="1" t="inlineStr">
         <is>
-          <t>ko.me.ˈsa.ɾãʊ̃</t>
+          <t>/ko.me.ˈsa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1362" s="1" t="inlineStr">
@@ -44360,7 +44376,7 @@
       </c>
       <c r="C1374" s="1" t="inlineStr">
         <is>
-          <t>ˈve.ẽỹ</t>
+          <t>/ˈve.ẽỹ/</t>
         </is>
       </c>
       <c r="D1374" s="1" t="inlineStr">
@@ -44803,7 +44819,7 @@
       </c>
       <c r="B1388" s="1" t="inlineStr">
         <is>
-          <t>[ˈkɔ.fɾi] 安全&lt;名&gt;</t>
+          <t>[ˈkɔ.fɾi] 保险箱；保险柜；金库&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1388" s="1" t="inlineStr">
@@ -44813,7 +44829,7 @@
       </c>
       <c r="D1388" s="1" t="inlineStr">
         <is>
-          <t>安全</t>
+          <t>保险箱；保险柜；金库</t>
         </is>
       </c>
       <c r="E1388" s="1" t="inlineStr">
@@ -45219,7 +45235,7 @@
       </c>
       <c r="B1401" s="1" t="inlineStr">
         <is>
-          <t>[a.ʁisˈka(ʁ)] 风险&lt;动&gt;</t>
+          <t>[a.ʁisˈka(ʁ)] 冒险；冒…的风险&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1401" s="1" t="inlineStr">
@@ -45229,7 +45245,7 @@
       </c>
       <c r="D1401" s="1" t="inlineStr">
         <is>
-          <t>风险</t>
+          <t>冒险；冒…的风险</t>
         </is>
       </c>
       <c r="E1401" s="1" t="inlineStr">
@@ -45635,7 +45651,7 @@
       </c>
       <c r="B1414" s="1" t="inlineStr">
         <is>
-          <t>[pɾĩˈsi.pju] 原则&lt;名&gt;</t>
+          <t>[/pɾĩˈsi.pju/] 开始&lt;名&gt;；开端&lt;名&gt;；原则&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1414" s="1" t="inlineStr">
@@ -45645,7 +45661,7 @@
       </c>
       <c r="D1414" s="1" t="inlineStr">
         <is>
-          <t>原则</t>
+          <t>开始&lt;名&gt;；开端&lt;名&gt;；原则&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1414" s="1" t="inlineStr">
@@ -45699,7 +45715,7 @@
       </c>
       <c r="B1416" s="1" t="inlineStr">
         <is>
-          <t>[paˈsej.u] 骑&lt;名&gt;</t>
+          <t>[paˈsej.u] 散步；游览；兜风&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1416" s="1" t="inlineStr">
@@ -45709,7 +45725,7 @@
       </c>
       <c r="D1416" s="1" t="inlineStr">
         <is>
-          <t>骑</t>
+          <t>散步；游览；兜风</t>
         </is>
       </c>
       <c r="E1416" s="1" t="inlineStr">
@@ -45960,7 +45976,7 @@
       </c>
       <c r="C1424" s="1" t="inlineStr">
         <is>
-          <t>a.ka.ˈba.ɾãʊ̃</t>
+          <t>/a.ka.ˈba.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1424" s="1" t="inlineStr">
@@ -45987,7 +46003,7 @@
       </c>
       <c r="B1425" s="1" t="inlineStr">
         <is>
-          <t>[ˈɡɔw.pi] 吹&lt;名&gt;</t>
+          <t>[ˈɡɔw.pi] 打击；一击；政变；骗局&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1425" s="1" t="inlineStr">
@@ -45997,7 +46013,7 @@
       </c>
       <c r="D1425" s="1" t="inlineStr">
         <is>
-          <t>吹</t>
+          <t>打击；一击；政变；骗局</t>
         </is>
       </c>
       <c r="E1425" s="1" t="inlineStr">
@@ -46403,7 +46419,7 @@
       </c>
       <c r="B1438" s="1" t="inlineStr">
         <is>
-          <t>[leˈʒẽ.dɐ] 标题&lt;名&gt;</t>
+          <t>[leˈʒẽ.dɐ] 字幕；图例；说明文字&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1438" s="1" t="inlineStr">
@@ -46413,7 +46429,7 @@
       </c>
       <c r="D1438" s="1" t="inlineStr">
         <is>
-          <t>标题</t>
+          <t>字幕；图例；说明文字</t>
         </is>
       </c>
       <c r="E1438" s="1" t="inlineStr">
@@ -46824,7 +46840,7 @@
       </c>
       <c r="C1451" s="1" t="inlineStr">
         <is>
-          <t>dʒi.ɾɛ.ta.ˈmẽ.tʃɪ</t>
+          <t>/dʒi.ɾɛ.ta.ˈmẽ.tʃɪ/</t>
         </is>
       </c>
       <c r="D1451" s="1" t="inlineStr">
@@ -47075,7 +47091,7 @@
       </c>
       <c r="B1459" s="1" t="inlineStr">
         <is>
-          <t>[vesˈt͡ʃi(ʁ)] 连衣裙&lt;动&gt;</t>
+          <t>[vesˈt͡ʃi(ʁ)] 穿；给…穿衣；穿着&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1459" s="1" t="inlineStr">
@@ -47085,7 +47101,7 @@
       </c>
       <c r="D1459" s="1" t="inlineStr">
         <is>
-          <t>连衣裙</t>
+          <t>穿；给…穿衣；穿着</t>
         </is>
       </c>
       <c r="E1459" s="1" t="inlineStr">
@@ -47107,7 +47123,7 @@
       </c>
       <c r="B1460" s="1" t="inlineStr">
         <is>
-          <t>[leˈva.du] 采取&lt;形&gt;</t>
+          <t>[leˈva.du] 被带走的；被携带的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C1460" s="1" t="inlineStr">
@@ -47117,7 +47133,7 @@
       </c>
       <c r="D1460" s="1" t="inlineStr">
         <is>
-          <t>采取</t>
+          <t>被带走的；被携带的</t>
         </is>
       </c>
       <c r="E1460" s="1" t="inlineStr">
@@ -47267,13 +47283,17 @@
       </c>
       <c r="B1465" s="1" t="inlineStr">
         <is>
-          <t>女孩&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C1465" s="1" t="inlineStr"/>
+          <t>[[ɡɐˈɾɔtɨ] 绞刑具；止血带；小公牛&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C1465" s="1" t="inlineStr">
+        <is>
+          <t>/ɡa.ˈɾɔ.t͡ʃi/</t>
+        </is>
+      </c>
       <c r="D1465" s="1" t="inlineStr">
         <is>
-          <t>女孩</t>
+          <t>绞刑具；止血带；小公牛</t>
         </is>
       </c>
       <c r="E1465" s="1" t="inlineStr">
@@ -47716,7 +47736,7 @@
       </c>
       <c r="C1479" s="1" t="inlineStr">
         <is>
-          <t>sɛˈɡʊ̃du</t>
+          <t>/sɛˈɡʊ̃du/</t>
         </is>
       </c>
       <c r="D1479" s="1" t="inlineStr">
@@ -47871,7 +47891,7 @@
       </c>
       <c r="B1484" s="1" t="inlineStr">
         <is>
-          <t>[a.siˈna(ʁ)] 标志&lt;动&gt;</t>
+          <t>[a.siˈna(ʁ)] 签署；签名&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1484" s="1" t="inlineStr">
@@ -47881,7 +47901,7 @@
       </c>
       <c r="D1484" s="1" t="inlineStr">
         <is>
-          <t>标志</t>
+          <t>签署；签名</t>
         </is>
       </c>
       <c r="E1484" s="1" t="inlineStr">
@@ -48351,7 +48371,7 @@
       </c>
       <c r="B1499" s="1" t="inlineStr">
         <is>
-          <t>[mẽ.t͡ʃiˈɾo.zu] 骗子&lt;名&gt;</t>
+          <t>[/mẽ.t͡ʃiˈɾo.zu/] 说谎的；爱撒谎的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1499" s="1" t="inlineStr">
@@ -48361,7 +48381,7 @@
       </c>
       <c r="D1499" s="1" t="inlineStr">
         <is>
-          <t>骗子</t>
+          <t>说谎的；爱撒谎的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1499" s="1" t="inlineStr">
@@ -48703,7 +48723,7 @@
       </c>
       <c r="B1510" s="1" t="inlineStr">
         <is>
-          <t>[paʁˈt͡ʃiw] 左&lt;叹&gt;</t>
+          <t>[paʁˈt͡ʃiw] 离开；出发；破裂&lt;叹&gt;</t>
         </is>
       </c>
       <c r="C1510" s="1" t="inlineStr">
@@ -48713,7 +48733,7 @@
       </c>
       <c r="D1510" s="1" t="inlineStr">
         <is>
-          <t>左</t>
+          <t>离开；出发；破裂</t>
         </is>
       </c>
       <c r="E1510" s="1" t="inlineStr">
@@ -48831,7 +48851,7 @@
       </c>
       <c r="B1514" s="1" t="inlineStr">
         <is>
-          <t>[d͡ʒi.ʒiˈta(ʁ)] 类型&lt;动&gt;</t>
+          <t>[d͡ʒi.ʒiˈta(ʁ)] 打字；键入；数字化&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1514" s="1" t="inlineStr">
@@ -48841,7 +48861,7 @@
       </c>
       <c r="D1514" s="1" t="inlineStr">
         <is>
-          <t>类型</t>
+          <t>打字；键入；数字化</t>
         </is>
       </c>
       <c r="E1514" s="1" t="inlineStr">
@@ -48959,7 +48979,7 @@
       </c>
       <c r="B1518" s="1" t="inlineStr">
         <is>
-          <t>[ˈɡoʁ.du] 脂肪&lt;名&gt;</t>
+          <t>[ˈɡoʁ.du] 胖的；肥胖的&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1518" s="1" t="inlineStr">
@@ -48969,7 +48989,7 @@
       </c>
       <c r="D1518" s="1" t="inlineStr">
         <is>
-          <t>脂肪</t>
+          <t>胖的；肥胖的</t>
         </is>
       </c>
       <c r="E1518" s="1" t="inlineStr">
@@ -49023,7 +49043,7 @@
       </c>
       <c r="B1520" s="1" t="inlineStr">
         <is>
-          <t>[dɨˈmɔ.ni.u] 恶魔&lt;名&gt;</t>
+          <t>[/dɨˈmɔ.ni.u/] 恶魔&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1520" s="1" t="inlineStr">
@@ -49033,7 +49053,7 @@
       </c>
       <c r="D1520" s="1" t="inlineStr">
         <is>
-          <t>恶魔</t>
+          <t>恶魔&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1520" s="1" t="inlineStr">
@@ -49087,7 +49107,7 @@
       </c>
       <c r="B1522" s="1" t="inlineStr">
         <is>
-          <t>[de.zeˈʒa(ʁ)] 愿望&lt;动&gt;</t>
+          <t>[de.zeˈʒa(ʁ)] 想要；希望；祝愿&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1522" s="1" t="inlineStr">
@@ -49097,7 +49117,7 @@
       </c>
       <c r="D1522" s="1" t="inlineStr">
         <is>
-          <t>愿望</t>
+          <t>想要；希望；祝愿</t>
         </is>
       </c>
       <c r="E1522" s="1" t="inlineStr">
@@ -49156,7 +49176,7 @@
       </c>
       <c r="C1524" s="1" t="inlineStr">
         <is>
-          <t>xow.ˈba.dʊ</t>
+          <t>/xow.ˈba.dʊ/</t>
         </is>
       </c>
       <c r="D1524" s="1" t="inlineStr">
@@ -49412,7 +49432,7 @@
       </c>
       <c r="C1532" s="1" t="inlineStr">
         <is>
-          <t>ow.ˈvi.ɾãʊ̃</t>
+          <t>/ow.ˈvi.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1532" s="1" t="inlineStr">
@@ -49567,7 +49587,7 @@
       </c>
       <c r="B1537" s="1" t="inlineStr">
         <is>
-          <t>[leˈva.ɾɐ̃w̃] 采取了&lt;动&gt;</t>
+          <t>[leˈva.ɾɐ̃w̃] 带走；拿走&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1537" s="1" t="inlineStr">
@@ -49577,7 +49597,7 @@
       </c>
       <c r="D1537" s="1" t="inlineStr">
         <is>
-          <t>采取了</t>
+          <t>带走；拿走</t>
         </is>
       </c>
       <c r="E1537" s="1" t="inlineStr">
@@ -50532,7 +50552,7 @@
       </c>
       <c r="C1567" s="1" t="inlineStr">
         <is>
-          <t>dʒi.ˈɾɛ.tʊ</t>
+          <t>/dʒi.ˈɾɛ.tʊ/</t>
         </is>
       </c>
       <c r="D1567" s="1" t="inlineStr">
@@ -50655,7 +50675,7 @@
       </c>
       <c r="B1571" s="1" t="inlineStr">
         <is>
-          <t>[peˈɾɐ̃.t͡ʃi] 之前&lt;介&gt;</t>
+          <t>[peˈɾɐ̃.t͡ʃi] 在…面前；面对&lt;介&gt;</t>
         </is>
       </c>
       <c r="C1571" s="1" t="inlineStr">
@@ -50665,7 +50685,7 @@
       </c>
       <c r="D1571" s="1" t="inlineStr">
         <is>
-          <t>之前</t>
+          <t>在…面前；面对</t>
         </is>
       </c>
       <c r="E1571" s="1" t="inlineStr">
@@ -50692,7 +50712,7 @@
       </c>
       <c r="C1572" s="1" t="inlineStr">
         <is>
-          <t>fĩ dʒi siˈmɐ̃na</t>
+          <t>/fĩ dʒi siˈmɐ̃na/</t>
         </is>
       </c>
       <c r="D1572" s="1" t="inlineStr">
@@ -51391,7 +51411,7 @@
       </c>
       <c r="B1594" s="1" t="inlineStr">
         <is>
-          <t>[ˈẽ.nɐ] 埃纳&lt;叹&gt;</t>
+          <t>[ˈẽ.nɐ] 哇；好家伙（表示惊讶、赞叹）&lt;叹&gt;</t>
         </is>
       </c>
       <c r="C1594" s="1" t="inlineStr">
@@ -51401,7 +51421,7 @@
       </c>
       <c r="D1594" s="1" t="inlineStr">
         <is>
-          <t>埃纳</t>
+          <t>哇；好家伙（表示惊讶、赞叹）</t>
         </is>
       </c>
       <c r="E1594" s="1" t="inlineStr">
@@ -51455,7 +51475,7 @@
       </c>
       <c r="B1596" s="1" t="inlineStr">
         <is>
-          <t>[ˈkɛ.dɐ] 秋天&lt;名&gt;</t>
+          <t>[ˈkɛ.dɐ] 落下；跌落；下降；倒台&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1596" s="1" t="inlineStr">
@@ -51465,7 +51485,7 @@
       </c>
       <c r="D1596" s="1" t="inlineStr">
         <is>
-          <t>秋天</t>
+          <t>落下；跌落；下降；倒台</t>
         </is>
       </c>
       <c r="E1596" s="1" t="inlineStr">
@@ -51647,7 +51667,7 @@
       </c>
       <c r="B1602" s="1" t="inlineStr">
         <is>
-          <t>[ˈʃɛ.ki] 检查&lt;名&gt;</t>
+          <t>[ˈʃɛ.ki] 支票&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1602" s="1" t="inlineStr">
@@ -51657,7 +51677,7 @@
       </c>
       <c r="D1602" s="1" t="inlineStr">
         <is>
-          <t>检查</t>
+          <t>支票</t>
         </is>
       </c>
       <c r="E1602" s="1" t="inlineStr">
@@ -51999,7 +52019,7 @@
       </c>
       <c r="B1613" s="1" t="inlineStr">
         <is>
-          <t>[ˈsɛ.lɐ] 细胞&lt;名&gt;</t>
+          <t>[ˈsɛ.lɐ] 牢房；囚室&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1613" s="1" t="inlineStr">
@@ -52009,7 +52029,7 @@
       </c>
       <c r="D1613" s="1" t="inlineStr">
         <is>
-          <t>细胞</t>
+          <t>牢房；囚室</t>
         </is>
       </c>
       <c r="E1613" s="1" t="inlineStr">
@@ -52292,7 +52312,7 @@
       </c>
       <c r="C1622" s="1" t="inlineStr">
         <is>
-          <t>ɛ</t>
+          <t>/ɛ/</t>
         </is>
       </c>
       <c r="D1622" s="1" t="inlineStr">
@@ -52415,7 +52435,7 @@
       </c>
       <c r="B1626" s="1" t="inlineStr">
         <is>
-          <t>[li.beʁˈta(ʁ)] 免费&lt;动&gt;</t>
+          <t>[li.beʁˈta(ʁ)] 解放；释放&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1626" s="1" t="inlineStr">
@@ -52425,7 +52445,7 @@
       </c>
       <c r="D1626" s="1" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>解放；释放</t>
         </is>
       </c>
       <c r="E1626" s="1" t="inlineStr">
@@ -52895,7 +52915,7 @@
       </c>
       <c r="B1641" s="1" t="inlineStr">
         <is>
-          <t>[kawˈza(ʁ)] 原因&lt;动&gt;</t>
+          <t>[kawˈza(ʁ)] 引起；导致；造成&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1641" s="1" t="inlineStr">
@@ -52905,7 +52925,7 @@
       </c>
       <c r="D1641" s="1" t="inlineStr">
         <is>
-          <t>原因</t>
+          <t>引起；导致；造成</t>
         </is>
       </c>
       <c r="E1641" s="1" t="inlineStr">
@@ -52927,7 +52947,7 @@
       </c>
       <c r="B1642" s="1" t="inlineStr">
         <is>
-          <t>[ʒẽˈt͡ʃiw] 温柔的&lt;形&gt;</t>
+          <t>[/ʒẽˈt͡ʃiw/] 亲切的；和蔼的&lt;形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1642" s="1" t="inlineStr">
@@ -52937,7 +52957,7 @@
       </c>
       <c r="D1642" s="1" t="inlineStr">
         <is>
-          <t>温柔的</t>
+          <t>亲切的；和蔼的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1642" s="1" t="inlineStr">
@@ -52964,7 +52984,7 @@
       </c>
       <c r="C1643" s="1" t="inlineStr">
         <is>
-          <t>big</t>
+          <t>/big/</t>
         </is>
       </c>
       <c r="D1643" s="1" t="inlineStr">
@@ -53119,7 +53139,7 @@
       </c>
       <c r="B1648" s="1" t="inlineStr">
         <is>
-          <t>[d͡ʒi.viˈzɐ̃w̃] 师&lt;名&gt;</t>
+          <t>[d͡ʒi.viˈzɐ̃w̃] 划分；分开；除法；部门；师（军队编制）&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1648" s="1" t="inlineStr">
@@ -53129,7 +53149,7 @@
       </c>
       <c r="D1648" s="1" t="inlineStr">
         <is>
-          <t>师</t>
+          <t>划分；分开；除法；部门；师（军队编制）</t>
         </is>
       </c>
       <c r="E1648" s="1" t="inlineStr">
@@ -53279,7 +53299,7 @@
       </c>
       <c r="B1653" s="1" t="inlineStr">
         <is>
-          <t>[ˈfũ.mu] 抽烟&lt;名&gt;</t>
+          <t>[ˈfũ.mu] 烟；烟雾&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1653" s="1" t="inlineStr">
@@ -53289,7 +53309,7 @@
       </c>
       <c r="D1653" s="1" t="inlineStr">
         <is>
-          <t>抽烟</t>
+          <t>烟；烟雾</t>
         </is>
       </c>
       <c r="E1653" s="1" t="inlineStr">
@@ -53407,7 +53427,7 @@
       </c>
       <c r="B1657" s="1" t="inlineStr">
         <is>
-          <t>[paˈdɾɐ̃w̃] 默认&lt;名&gt;</t>
+          <t>[/paˈdɾɐ̃w̃/] 标准；模式；图案&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1657" s="1" t="inlineStr">
@@ -53417,7 +53437,7 @@
       </c>
       <c r="D1657" s="1" t="inlineStr">
         <is>
-          <t>默认</t>
+          <t>标准；模式；图案&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1657" s="1" t="inlineStr">
@@ -53471,7 +53491,7 @@
       </c>
       <c r="B1659" s="1" t="inlineStr">
         <is>
-          <t>[kõ.seˈɡi.ɾɐ̃w̃] 明白了&lt;动&gt;</t>
+          <t>[kõ.seˈɡi.ɾɐ̃w̃] 做到；获得；成功&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1659" s="1" t="inlineStr">
@@ -53481,7 +53501,7 @@
       </c>
       <c r="D1659" s="1" t="inlineStr">
         <is>
-          <t>明白了</t>
+          <t>做到；获得；成功</t>
         </is>
       </c>
       <c r="E1659" s="1" t="inlineStr">
@@ -53759,7 +53779,7 @@
       </c>
       <c r="B1668" s="1" t="inlineStr">
         <is>
-          <t>[ko.meˈte(ʁ)] 提交&lt;动&gt;</t>
+          <t>[ko.meˈte(ʁ)] 犯（错误、罪行）&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1668" s="1" t="inlineStr">
@@ -53769,7 +53789,7 @@
       </c>
       <c r="D1668" s="1" t="inlineStr">
         <is>
-          <t>提交</t>
+          <t>犯（错误、罪行）</t>
         </is>
       </c>
       <c r="E1668" s="1" t="inlineStr">
@@ -54111,7 +54131,7 @@
       </c>
       <c r="B1679" s="1" t="inlineStr">
         <is>
-          <t>[is.t͡ʃiˈvɛ.ɾɐ̃w̃] 已经&lt;动&gt;</t>
+          <t>[is.t͡ʃiˈvɛ.ɾɐ̃w̃] 在；处于；是&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1679" s="1" t="inlineStr">
@@ -54121,7 +54141,7 @@
       </c>
       <c r="D1679" s="1" t="inlineStr">
         <is>
-          <t>已经</t>
+          <t>在；处于；是</t>
         </is>
       </c>
       <c r="E1679" s="1" t="inlineStr">
@@ -54239,7 +54259,7 @@
       </c>
       <c r="B1683" s="1" t="inlineStr">
         <is>
-          <t>[kõ.biˈna.du] 合并的&lt;名&gt;</t>
+          <t>[/kõ.biˈna.du/] 约定好的；商定的&lt;形&gt;；约定&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1683" s="1" t="inlineStr">
@@ -54249,7 +54269,7 @@
       </c>
       <c r="D1683" s="1" t="inlineStr">
         <is>
-          <t>合并的</t>
+          <t>约定好的；商定的&lt;形&gt;；约定&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1683" s="1" t="inlineStr">
@@ -54911,7 +54931,7 @@
       </c>
       <c r="B1704" s="1" t="inlineStr">
         <is>
-          <t>[ˈtuʁ.nu] 转变&lt;名&gt;</t>
+          <t>[ˈtuʁ.nu] 班次；轮班；轮流&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1704" s="1" t="inlineStr">
@@ -54921,7 +54941,7 @@
       </c>
       <c r="D1704" s="1" t="inlineStr">
         <is>
-          <t>转变</t>
+          <t>班次；轮班；轮流</t>
         </is>
       </c>
       <c r="E1704" s="1" t="inlineStr">
@@ -55103,7 +55123,7 @@
       </c>
       <c r="B1710" s="1" t="inlineStr">
         <is>
-          <t>[ku.zĩˈɲa(ʁ)] 厨师&lt;动&gt;</t>
+          <t>[ku.zĩˈɲa(ʁ)] 烹调；烹饪&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1710" s="1" t="inlineStr">
@@ -55113,7 +55133,7 @@
       </c>
       <c r="D1710" s="1" t="inlineStr">
         <is>
-          <t>厨师</t>
+          <t>烹调；烹饪</t>
         </is>
       </c>
       <c r="E1710" s="1" t="inlineStr">
@@ -55199,7 +55219,7 @@
       </c>
       <c r="B1713" s="1" t="inlineStr">
         <is>
-          <t>[saˈi.du] 左&lt;形&gt;</t>
+          <t>[saˈi.du] 离开；出去&lt;形&gt;</t>
         </is>
       </c>
       <c r="C1713" s="1" t="inlineStr">
@@ -55209,7 +55229,7 @@
       </c>
       <c r="D1713" s="1" t="inlineStr">
         <is>
-          <t>左</t>
+          <t>离开；出去</t>
         </is>
       </c>
       <c r="E1713" s="1" t="inlineStr">
@@ -55330,7 +55350,11 @@
           <t>蒂姆&lt;叹&gt;</t>
         </is>
       </c>
-      <c r="C1717" s="1" t="inlineStr"/>
+      <c r="C1717" s="1" t="inlineStr">
+        <is>
+          <t>/tĩ/</t>
+        </is>
+      </c>
       <c r="D1717" s="1" t="inlineStr">
         <is>
           <t>蒂姆</t>
@@ -55579,17 +55603,17 @@
       </c>
       <c r="B1725" s="1" t="inlineStr">
         <is>
-          <t>[dey.ˈʃa.ɾãʊ̃] 左&lt;动&gt;</t>
+          <t>[dey.ˈʃa.ɾãʊ̃] 离开；留下；让；放弃&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1725" s="1" t="inlineStr">
         <is>
-          <t>dey.ˈʃa.ɾãʊ̃</t>
+          <t>/dey.ˈʃa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1725" s="1" t="inlineStr">
         <is>
-          <t>左</t>
+          <t>离开；留下；让；放弃</t>
         </is>
       </c>
       <c r="E1725" s="1" t="inlineStr">
@@ -56539,7 +56563,7 @@
       </c>
       <c r="B1755" s="1" t="inlineStr">
         <is>
-          <t>[a.suˈmi(ʁ)] 假设&lt;动&gt;</t>
+          <t>[/a.suˈmi(ʁ)/] 承担；担任&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1755" s="1" t="inlineStr">
@@ -56549,7 +56573,7 @@
       </c>
       <c r="D1755" s="1" t="inlineStr">
         <is>
-          <t>假设</t>
+          <t>承担；担任&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1755" s="1" t="inlineStr">
@@ -56635,7 +56659,7 @@
       </c>
       <c r="B1758" s="1" t="inlineStr">
         <is>
-          <t>[tɾejˈna(ʁ)] 火车&lt;动&gt;</t>
+          <t>[tɾejˈna(ʁ)] 训练；锻炼&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1758" s="1" t="inlineStr">
@@ -56645,7 +56669,7 @@
       </c>
       <c r="D1758" s="1" t="inlineStr">
         <is>
-          <t>火车</t>
+          <t>训练；锻炼</t>
         </is>
       </c>
       <c r="E1758" s="1" t="inlineStr">
@@ -56768,7 +56792,7 @@
       </c>
       <c r="C1762" s="1" t="inlineStr">
         <is>
-          <t>seˈɲoɾ</t>
+          <t>/seˈɲoɾ/</t>
         </is>
       </c>
       <c r="D1762" s="1" t="inlineStr">
@@ -56864,7 +56888,7 @@
       </c>
       <c r="C1765" s="1" t="inlineStr">
         <is>
-          <t>ˈfũ.dʊs</t>
+          <t>/ˈfũ.dʊs/</t>
         </is>
       </c>
       <c r="D1765" s="1" t="inlineStr">
@@ -56923,7 +56947,7 @@
       </c>
       <c r="B1767" s="1" t="inlineStr">
         <is>
-          <t>[me.d͡ʒi.kaˈmẽ.tu] 医学&lt;名&gt;</t>
+          <t>[me.d͡ʒi.kaˈmẽ.tu] 药物；药品&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1767" s="1" t="inlineStr">
@@ -56933,7 +56957,7 @@
       </c>
       <c r="D1767" s="1" t="inlineStr">
         <is>
-          <t>医学</t>
+          <t>药物；药品</t>
         </is>
       </c>
       <c r="E1767" s="1" t="inlineStr">
@@ -57179,7 +57203,7 @@
       </c>
       <c r="B1775" s="1" t="inlineStr">
         <is>
-          <t>[ˈku.peʁ] 库珀&lt;名&gt;</t>
+          <t>[/ˈku.peʁ/] 库珀测试（一种耐力跑体能测试）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1775" s="1" t="inlineStr">
@@ -57189,7 +57213,7 @@
       </c>
       <c r="D1775" s="1" t="inlineStr">
         <is>
-          <t>库珀</t>
+          <t>库珀测试（一种耐力跑体能测试）</t>
         </is>
       </c>
       <c r="E1775" s="1" t="inlineStr">
@@ -57211,7 +57235,7 @@
       </c>
       <c r="B1776" s="1" t="inlineStr">
         <is>
-          <t>[ˈfɐ̃] 风扇&lt;名&gt;</t>
+          <t>[ˈfɐ̃] 粉丝；爱好者&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1776" s="1" t="inlineStr">
@@ -57221,7 +57245,7 @@
       </c>
       <c r="D1776" s="1" t="inlineStr">
         <is>
-          <t>风扇</t>
+          <t>粉丝；爱好者</t>
         </is>
       </c>
       <c r="E1776" s="1" t="inlineStr">
@@ -57339,7 +57363,7 @@
       </c>
       <c r="B1780" s="1" t="inlineStr">
         <is>
-          <t>[ˈpõ.tɐ] 小费&lt;名&gt;</t>
+          <t>[ˈpõ.tɐ] 尖端；末端&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1780" s="1" t="inlineStr">
@@ -57349,7 +57373,7 @@
       </c>
       <c r="D1780" s="1" t="inlineStr">
         <is>
-          <t>小费</t>
+          <t>尖端；末端</t>
         </is>
       </c>
       <c r="E1780" s="1" t="inlineStr">
@@ -57403,7 +57427,7 @@
       </c>
       <c r="B1782" s="1" t="inlineStr">
         <is>
-          <t>[a.li.mẽˈta(ʁ)] 饲料&lt;动&gt;</t>
+          <t>[a.li.mẽˈta(ʁ)] 喂养；供养&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1782" s="1" t="inlineStr">
@@ -57413,7 +57437,7 @@
       </c>
       <c r="D1782" s="1" t="inlineStr">
         <is>
-          <t>饲料</t>
+          <t>喂养；供养</t>
         </is>
       </c>
       <c r="E1782" s="1" t="inlineStr">
@@ -57723,7 +57747,7 @@
       </c>
       <c r="B1792" s="1" t="inlineStr">
         <is>
-          <t>[sẽ.ɲoˈɾi.tɐ] 想念&lt;名&gt;</t>
+          <t>[sẽ.ɲoˈɾi.tɐ] 小姐；年轻女士&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1792" s="1" t="inlineStr">
@@ -57733,7 +57757,7 @@
       </c>
       <c r="D1792" s="1" t="inlineStr">
         <is>
-          <t>想念</t>
+          <t>小姐；年轻女士</t>
         </is>
       </c>
       <c r="E1792" s="1" t="inlineStr">
@@ -58560,7 +58584,7 @@
       </c>
       <c r="C1818" s="1" t="inlineStr">
         <is>
-          <t>ˈkɔ.li</t>
+          <t>/ˈkɔ.li/</t>
         </is>
       </c>
       <c r="D1818" s="1" t="inlineStr">
@@ -58907,7 +58931,7 @@
       </c>
       <c r="B1829" s="1" t="inlineStr">
         <is>
-          <t>[ma.ɾaˈvi.ʎɐ] 想知道&lt;名&gt;</t>
+          <t>[ma.ɾaˈvi.ʎɐ] 奇迹；奇观&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1829" s="1" t="inlineStr">
@@ -58917,7 +58941,7 @@
       </c>
       <c r="D1829" s="1" t="inlineStr">
         <is>
-          <t>想知道</t>
+          <t>奇迹；奇观</t>
         </is>
       </c>
       <c r="E1829" s="1" t="inlineStr">
@@ -58971,7 +58995,7 @@
       </c>
       <c r="B1831" s="1" t="inlineStr">
         <is>
-          <t>[ˈpu.tu] 生气了&lt;名&gt;</t>
+          <t>[ˈpu.tu] 男孩；小孩&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1831" s="1" t="inlineStr">
@@ -58981,7 +59005,7 @@
       </c>
       <c r="D1831" s="1" t="inlineStr">
         <is>
-          <t>生气了</t>
+          <t>男孩；小孩</t>
         </is>
       </c>
       <c r="E1831" s="1" t="inlineStr">
@@ -59003,7 +59027,7 @@
       </c>
       <c r="B1832" s="1" t="inlineStr">
         <is>
-          <t>[ˈpuw.su] 脉冲&lt;名&gt;</t>
+          <t>[/ˈpuw.su/] 脉搏；手腕&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1832" s="1" t="inlineStr">
@@ -59013,7 +59037,7 @@
       </c>
       <c r="D1832" s="1" t="inlineStr">
         <is>
-          <t>脉冲</t>
+          <t>脉搏；手腕&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1832" s="1" t="inlineStr">
@@ -60059,7 +60083,7 @@
       </c>
       <c r="B1865" s="1" t="inlineStr">
         <is>
-          <t>[ˈfɔw.ɡɐ] 松弛&lt;名&gt;</t>
+          <t>[/ˈfɔw.ɡɐ/] 闲暇；休息日&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1865" s="1" t="inlineStr">
@@ -60069,7 +60093,7 @@
       </c>
       <c r="D1865" s="1" t="inlineStr">
         <is>
-          <t>松弛</t>
+          <t>闲暇；休息日</t>
         </is>
       </c>
       <c r="E1865" s="1" t="inlineStr">
@@ -60443,7 +60467,7 @@
       </c>
       <c r="B1877" s="1" t="inlineStr">
         <is>
-          <t>[fiwˈma(ʁ)] 电影&lt;动&gt;</t>
+          <t>[fiwˈma(ʁ)] 拍摄；摄制&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1877" s="1" t="inlineStr">
@@ -60453,7 +60477,7 @@
       </c>
       <c r="D1877" s="1" t="inlineStr">
         <is>
-          <t>电影</t>
+          <t>拍摄；摄制</t>
         </is>
       </c>
       <c r="E1877" s="1" t="inlineStr">
@@ -60731,7 +60755,7 @@
       </c>
       <c r="B1886" s="1" t="inlineStr">
         <is>
-          <t>[ˈʒi.ɾɐ] 旋转&lt;名&gt;</t>
+          <t>[/ˈʒi.ɾɐ/] 漂亮的&lt;形&gt;（亦为girar的第三人称单数变位）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1886" s="1" t="inlineStr">
@@ -60741,7 +60765,7 @@
       </c>
       <c r="D1886" s="1" t="inlineStr">
         <is>
-          <t>旋转</t>
+          <t>漂亮的&lt;形&gt;（亦为girar的第三人称单数变位）</t>
         </is>
       </c>
       <c r="E1886" s="1" t="inlineStr">
@@ -61086,7 +61110,11 @@
           <t>行动&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1897" s="1" t="inlineStr"/>
+      <c r="C1897" s="1" t="inlineStr">
+        <is>
+          <t>/ˈak.tu/</t>
+        </is>
+      </c>
       <c r="D1897" s="1" t="inlineStr">
         <is>
           <t>行动</t>
@@ -61623,7 +61651,7 @@
       </c>
       <c r="B1914" s="1" t="inlineStr">
         <is>
-          <t>[ˈmĩ.nɐ] 我的&lt;名&gt;</t>
+          <t>[ˈmĩ.nɐ] 矿山；矿井；地雷&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1914" s="1" t="inlineStr">
@@ -61633,7 +61661,7 @@
       </c>
       <c r="D1914" s="1" t="inlineStr">
         <is>
-          <t>我的</t>
+          <t>矿山；矿井；地雷</t>
         </is>
       </c>
       <c r="E1914" s="1" t="inlineStr">
@@ -61911,7 +61939,7 @@
       </c>
       <c r="B1923" s="1" t="inlineStr">
         <is>
-          <t>[ˈkaʁ.ɡu] 位置&lt;名&gt;</t>
+          <t>[ˈkaʁ.ɡu] 职位；职务&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1923" s="1" t="inlineStr">
@@ -61921,7 +61949,7 @@
       </c>
       <c r="D1923" s="1" t="inlineStr">
         <is>
-          <t>位置</t>
+          <t>职位；职务</t>
         </is>
       </c>
       <c r="E1923" s="1" t="inlineStr">
@@ -61975,7 +62003,7 @@
       </c>
       <c r="B1925" s="1" t="inlineStr">
         <is>
-          <t>[aw.d͡ʒiˈẽ.sjɐ] 观众&lt;名&gt;</t>
+          <t>[/aw.d͡ʒiˈẽ.sjɐ/] 听众；接见；收视率&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1925" s="1" t="inlineStr">
@@ -61985,7 +62013,7 @@
       </c>
       <c r="D1925" s="1" t="inlineStr">
         <is>
-          <t>观众</t>
+          <t>听众；接见；收视率&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1925" s="1" t="inlineStr">
@@ -62039,7 +62067,7 @@
       </c>
       <c r="B1927" s="1" t="inlineStr">
         <is>
-          <t>[ˈbɔ.tɐ] 启动&lt;名&gt;</t>
+          <t>[ˈbɔ.tɐ] 靴子&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1927" s="1" t="inlineStr">
@@ -62049,7 +62077,7 @@
       </c>
       <c r="D1927" s="1" t="inlineStr">
         <is>
-          <t>启动</t>
+          <t>靴子</t>
         </is>
       </c>
       <c r="E1927" s="1" t="inlineStr">
@@ -62327,7 +62355,7 @@
       </c>
       <c r="B1936" s="1" t="inlineStr">
         <is>
-          <t>[a.sisˈt͡ʃi(ʁ)] 手表&lt;动&gt;</t>
+          <t>[a.sisˈt͡ʃi(ʁ)] 观看；出席&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1936" s="1" t="inlineStr">
@@ -62337,7 +62365,7 @@
       </c>
       <c r="D1936" s="1" t="inlineStr">
         <is>
-          <t>手表</t>
+          <t>观看；出席</t>
         </is>
       </c>
       <c r="E1936" s="1" t="inlineStr">
@@ -63703,7 +63731,7 @@
       </c>
       <c r="B1979" s="1" t="inlineStr">
         <is>
-          <t>[ˈsẽ.tu] 分&lt;名&gt;</t>
+          <t>[ˈsẽ.tu] 一百&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1979" s="1" t="inlineStr">
@@ -63713,7 +63741,7 @@
       </c>
       <c r="D1979" s="1" t="inlineStr">
         <is>
-          <t>分</t>
+          <t>一百</t>
         </is>
       </c>
       <c r="E1979" s="1" t="inlineStr">
@@ -63804,7 +63832,7 @@
       </c>
       <c r="C1982" s="1" t="inlineStr">
         <is>
-          <t>de.za.pa.ɾe.ˈse.ɾãʊ̃</t>
+          <t>/de.za.pa.ɾe.ˈse.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1982" s="1" t="inlineStr">
@@ -63895,7 +63923,7 @@
       </c>
       <c r="B1985" s="1" t="inlineStr">
         <is>
-          <t>[ˈla.tɐ] 可以&lt;名&gt;</t>
+          <t>[ˈla.tɐ] 罐；罐头盒&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1985" s="1" t="inlineStr">
@@ -63905,7 +63933,7 @@
       </c>
       <c r="D1985" s="1" t="inlineStr">
         <is>
-          <t>可以</t>
+          <t>罐；罐头盒</t>
         </is>
       </c>
       <c r="E1985" s="1" t="inlineStr">
@@ -64151,7 +64179,7 @@
       </c>
       <c r="B1993" s="1" t="inlineStr">
         <is>
-          <t>[liˈvɾa(ʁ)] 免费&lt;动&gt;</t>
+          <t>[liˈvɾa(ʁ)] 使摆脱；解救；释放&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1993" s="1" t="inlineStr">
@@ -64161,7 +64189,7 @@
       </c>
       <c r="D1993" s="1" t="inlineStr">
         <is>
-          <t>免费</t>
+          <t>使摆脱；解救；释放</t>
         </is>
       </c>
       <c r="E1993" s="1" t="inlineStr">
@@ -64279,7 +64307,7 @@
       </c>
       <c r="B1997" s="1" t="inlineStr">
         <is>
-          <t>[kusˈtũ.mi] 定制&lt;名&gt;</t>
+          <t>[kusˈtũ.mi] 习俗；习惯&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1997" s="1" t="inlineStr">
@@ -64289,7 +64317,7 @@
       </c>
       <c r="D1997" s="1" t="inlineStr">
         <is>
-          <t>定制</t>
+          <t>习俗；习惯</t>
         </is>
       </c>
       <c r="E1997" s="1" t="inlineStr">
